--- a/data/store_info.xlsx
+++ b/data/store_info.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeff0\OneDrive\桌面\115_NTUT_Thesis\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8528CE6-8022-444C-84EB-6AFD62205D4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{743D5722-6E06-4CA8-A135-C52C58AA1AB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9459" uniqueCount="3641">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9494" uniqueCount="3652">
   <si>
     <t>店鋪編號</t>
   </si>
@@ -10949,6 +10949,50 @@
   </si>
   <si>
     <t>新北市淡水區水源街二段177巷67號</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>新莊中港店</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>林口DC</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>新北市新莊區中港路126號</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>新北市三重區中華路53號</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>三重華泰店</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>桃園市龜山區復興街5號</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>龜山文醫店</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>新北市淡水區民生路119號</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>淡水民生店</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>臺北市北投區立德路8號2樓</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>關渡慈濟店</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -11375,19 +11419,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M729"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M734"/>
+  <sheetFormatPr defaultRowHeight="16.149999999999999" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.125" customWidth="1"/>
-    <col min="3" max="3" width="13.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="69.375" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="18.375" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.86328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.1328125" customWidth="1"/>
+    <col min="3" max="3" width="13.86328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="69.3984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="18.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="9.46484375" bestFit="1" customWidth="1"/>
     <col min="11" max="13" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -11428,7 +11472,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
@@ -11469,7 +11513,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>23</v>
       </c>
@@ -11510,7 +11554,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>28</v>
       </c>
@@ -11551,7 +11595,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>33</v>
       </c>
@@ -11592,7 +11636,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
         <v>38</v>
       </c>
@@ -11633,7 +11677,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
         <v>43</v>
       </c>
@@ -11674,7 +11718,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
         <v>48</v>
       </c>
@@ -11715,7 +11759,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
         <v>53</v>
       </c>
@@ -11756,7 +11800,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
         <v>58</v>
       </c>
@@ -11797,7 +11841,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
         <v>63</v>
       </c>
@@ -11838,7 +11882,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
         <v>68</v>
       </c>
@@ -11879,7 +11923,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
         <v>73</v>
       </c>
@@ -11920,7 +11964,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
         <v>78</v>
       </c>
@@ -11961,7 +12005,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
         <v>83</v>
       </c>
@@ -12002,7 +12046,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
         <v>88</v>
       </c>
@@ -12043,7 +12087,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
         <v>93</v>
       </c>
@@ -12084,7 +12128,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
         <v>98</v>
       </c>
@@ -12125,7 +12169,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
         <v>103</v>
       </c>
@@ -12166,7 +12210,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
         <v>108</v>
       </c>
@@ -12207,7 +12251,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
         <v>113</v>
       </c>
@@ -12248,7 +12292,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
         <v>118</v>
       </c>
@@ -12289,7 +12333,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
         <v>123</v>
       </c>
@@ -12330,7 +12374,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="s">
         <v>128</v>
       </c>
@@ -12371,7 +12415,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
         <v>133</v>
       </c>
@@ -12412,7 +12456,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A26" s="1" t="s">
         <v>138</v>
       </c>
@@ -12453,7 +12497,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A27" s="1" t="s">
         <v>143</v>
       </c>
@@ -12494,7 +12538,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A28" s="1" t="s">
         <v>148</v>
       </c>
@@ -12535,7 +12579,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A29" s="1" t="s">
         <v>153</v>
       </c>
@@ -12576,7 +12620,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A30" s="1" t="s">
         <v>158</v>
       </c>
@@ -12617,7 +12661,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A31" s="1" t="s">
         <v>163</v>
       </c>
@@ -12658,7 +12702,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A32" s="1" t="s">
         <v>168</v>
       </c>
@@ -12699,7 +12743,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A33" s="1" t="s">
         <v>173</v>
       </c>
@@ -12740,7 +12784,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A34" s="1" t="s">
         <v>178</v>
       </c>
@@ -12781,7 +12825,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A35" s="1" t="s">
         <v>183</v>
       </c>
@@ -12822,7 +12866,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A36" s="1" t="s">
         <v>188</v>
       </c>
@@ -12863,7 +12907,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A37" s="1" t="s">
         <v>193</v>
       </c>
@@ -12904,7 +12948,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A38" s="1" t="s">
         <v>198</v>
       </c>
@@ -12945,7 +12989,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A39" s="1" t="s">
         <v>203</v>
       </c>
@@ -12986,7 +13030,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A40" s="1" t="s">
         <v>208</v>
       </c>
@@ -13027,7 +13071,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A41" s="1" t="s">
         <v>213</v>
       </c>
@@ -13068,7 +13112,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A42" s="1" t="s">
         <v>218</v>
       </c>
@@ -13109,7 +13153,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A43" s="1" t="s">
         <v>223</v>
       </c>
@@ -13150,7 +13194,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A44" s="1" t="s">
         <v>228</v>
       </c>
@@ -13191,7 +13235,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A45" s="1" t="s">
         <v>233</v>
       </c>
@@ -13232,7 +13276,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A46" s="1" t="s">
         <v>238</v>
       </c>
@@ -13273,7 +13317,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A47" s="1" t="s">
         <v>243</v>
       </c>
@@ -13314,7 +13358,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A48" s="1" t="s">
         <v>248</v>
       </c>
@@ -13355,7 +13399,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A49" s="1" t="s">
         <v>253</v>
       </c>
@@ -13396,7 +13440,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A50" s="1" t="s">
         <v>258</v>
       </c>
@@ -13437,7 +13481,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A51" s="1" t="s">
         <v>263</v>
       </c>
@@ -13478,7 +13522,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A52" s="1" t="s">
         <v>268</v>
       </c>
@@ -13519,7 +13563,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A53" s="1" t="s">
         <v>273</v>
       </c>
@@ -13560,7 +13604,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A54" s="1" t="s">
         <v>278</v>
       </c>
@@ -13601,7 +13645,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A55" s="1" t="s">
         <v>283</v>
       </c>
@@ -13642,7 +13686,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A56" s="1" t="s">
         <v>288</v>
       </c>
@@ -13683,7 +13727,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A57" s="1" t="s">
         <v>293</v>
       </c>
@@ -13724,7 +13768,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A58" s="1" t="s">
         <v>298</v>
       </c>
@@ -13765,7 +13809,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A59" s="1" t="s">
         <v>303</v>
       </c>
@@ -13806,7 +13850,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A60" s="1" t="s">
         <v>308</v>
       </c>
@@ -13847,7 +13891,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A61" s="1" t="s">
         <v>313</v>
       </c>
@@ -13888,7 +13932,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A62" s="1" t="s">
         <v>318</v>
       </c>
@@ -13929,7 +13973,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A63" s="1" t="s">
         <v>323</v>
       </c>
@@ -13970,7 +14014,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A64" s="1" t="s">
         <v>328</v>
       </c>
@@ -14011,7 +14055,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A65" s="1" t="s">
         <v>333</v>
       </c>
@@ -14052,7 +14096,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A66" s="1" t="s">
         <v>338</v>
       </c>
@@ -14093,7 +14137,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A67" s="1" t="s">
         <v>343</v>
       </c>
@@ -14134,7 +14178,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A68" s="1" t="s">
         <v>348</v>
       </c>
@@ -14175,7 +14219,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A69" s="1" t="s">
         <v>353</v>
       </c>
@@ -14216,7 +14260,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A70" s="1" t="s">
         <v>358</v>
       </c>
@@ -14257,7 +14301,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A71" s="1" t="s">
         <v>363</v>
       </c>
@@ -14298,7 +14342,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A72" s="1" t="s">
         <v>368</v>
       </c>
@@ -14339,7 +14383,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A73" s="1" t="s">
         <v>373</v>
       </c>
@@ -14380,7 +14424,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A74" s="1" t="s">
         <v>378</v>
       </c>
@@ -14421,7 +14465,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A75" s="1" t="s">
         <v>383</v>
       </c>
@@ -14462,7 +14506,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A76" s="1" t="s">
         <v>388</v>
       </c>
@@ -14503,7 +14547,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A77" s="1" t="s">
         <v>393</v>
       </c>
@@ -14544,7 +14588,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A78" s="1" t="s">
         <v>398</v>
       </c>
@@ -14585,7 +14629,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A79" s="1" t="s">
         <v>403</v>
       </c>
@@ -14626,7 +14670,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A80" s="1" t="s">
         <v>408</v>
       </c>
@@ -14667,7 +14711,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A81" s="1" t="s">
         <v>413</v>
       </c>
@@ -14708,7 +14752,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A82" s="1" t="s">
         <v>418</v>
       </c>
@@ -14749,7 +14793,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A83" s="1" t="s">
         <v>423</v>
       </c>
@@ -14790,7 +14834,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A84" s="1" t="s">
         <v>428</v>
       </c>
@@ -14831,7 +14875,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A85" s="1" t="s">
         <v>433</v>
       </c>
@@ -14872,7 +14916,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A86" s="1" t="s">
         <v>438</v>
       </c>
@@ -14913,7 +14957,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A87" s="1" t="s">
         <v>443</v>
       </c>
@@ -14954,7 +14998,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A88" s="1" t="s">
         <v>448</v>
       </c>
@@ -14995,7 +15039,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A89" s="1" t="s">
         <v>453</v>
       </c>
@@ -15036,7 +15080,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A90" s="1" t="s">
         <v>458</v>
       </c>
@@ -15077,7 +15121,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A91" s="1" t="s">
         <v>463</v>
       </c>
@@ -15118,7 +15162,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A92" s="1" t="s">
         <v>468</v>
       </c>
@@ -15159,7 +15203,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A93" s="1" t="s">
         <v>473</v>
       </c>
@@ -15200,7 +15244,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A94" s="1" t="s">
         <v>478</v>
       </c>
@@ -15241,7 +15285,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A95" s="1" t="s">
         <v>483</v>
       </c>
@@ -15282,7 +15326,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A96" s="1" t="s">
         <v>488</v>
       </c>
@@ -15323,7 +15367,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A97" s="1" t="s">
         <v>493</v>
       </c>
@@ -15364,7 +15408,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A98" s="1" t="s">
         <v>498</v>
       </c>
@@ -15405,7 +15449,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A99" s="1" t="s">
         <v>503</v>
       </c>
@@ -15446,7 +15490,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A100" s="1" t="s">
         <v>508</v>
       </c>
@@ -15487,7 +15531,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A101" s="1" t="s">
         <v>513</v>
       </c>
@@ -15528,7 +15572,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A102" s="1" t="s">
         <v>518</v>
       </c>
@@ -15569,7 +15613,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A103" s="1" t="s">
         <v>523</v>
       </c>
@@ -15610,7 +15654,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A104" s="1" t="s">
         <v>528</v>
       </c>
@@ -15651,7 +15695,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A105" s="1" t="s">
         <v>533</v>
       </c>
@@ -15692,7 +15736,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A106" s="1" t="s">
         <v>538</v>
       </c>
@@ -15733,7 +15777,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A107" s="1" t="s">
         <v>543</v>
       </c>
@@ -15774,7 +15818,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A108" s="1" t="s">
         <v>548</v>
       </c>
@@ -15815,7 +15859,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A109" s="1" t="s">
         <v>553</v>
       </c>
@@ -15856,7 +15900,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A110" s="1" t="s">
         <v>558</v>
       </c>
@@ -15897,7 +15941,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A111" s="1" t="s">
         <v>563</v>
       </c>
@@ -15938,7 +15982,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A112" s="1" t="s">
         <v>568</v>
       </c>
@@ -15979,7 +16023,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A113" s="1" t="s">
         <v>573</v>
       </c>
@@ -16020,7 +16064,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A114" s="1" t="s">
         <v>578</v>
       </c>
@@ -16061,7 +16105,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A115" s="1" t="s">
         <v>583</v>
       </c>
@@ -16102,7 +16146,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A116" s="1" t="s">
         <v>588</v>
       </c>
@@ -16143,7 +16187,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A117" s="1" t="s">
         <v>593</v>
       </c>
@@ -16184,7 +16228,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A118" s="1" t="s">
         <v>598</v>
       </c>
@@ -16225,7 +16269,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A119" s="1" t="s">
         <v>603</v>
       </c>
@@ -16266,7 +16310,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A120" s="1" t="s">
         <v>608</v>
       </c>
@@ -16307,7 +16351,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A121" s="1" t="s">
         <v>613</v>
       </c>
@@ -16348,7 +16392,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A122" s="1" t="s">
         <v>618</v>
       </c>
@@ -16389,7 +16433,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A123" s="1" t="s">
         <v>623</v>
       </c>
@@ -16430,7 +16474,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A124" s="1" t="s">
         <v>628</v>
       </c>
@@ -16471,7 +16515,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A125" s="1" t="s">
         <v>633</v>
       </c>
@@ -16512,7 +16556,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A126" s="1" t="s">
         <v>638</v>
       </c>
@@ -16553,7 +16597,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A127" s="1" t="s">
         <v>643</v>
       </c>
@@ -16594,7 +16638,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A128" s="1" t="s">
         <v>648</v>
       </c>
@@ -16635,7 +16679,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A129" s="1" t="s">
         <v>653</v>
       </c>
@@ -16676,7 +16720,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A130" s="1" t="s">
         <v>658</v>
       </c>
@@ -16717,7 +16761,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A131" s="1" t="s">
         <v>663</v>
       </c>
@@ -16758,7 +16802,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A132" s="1" t="s">
         <v>668</v>
       </c>
@@ -16799,7 +16843,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A133" s="1" t="s">
         <v>673</v>
       </c>
@@ -16840,7 +16884,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A134" s="1" t="s">
         <v>678</v>
       </c>
@@ -16881,7 +16925,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A135" s="1" t="s">
         <v>683</v>
       </c>
@@ -16922,7 +16966,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A136" s="1" t="s">
         <v>688</v>
       </c>
@@ -16963,7 +17007,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A137" s="1" t="s">
         <v>693</v>
       </c>
@@ -17004,7 +17048,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A138" s="1" t="s">
         <v>698</v>
       </c>
@@ -17045,7 +17089,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A139" s="1" t="s">
         <v>703</v>
       </c>
@@ -17086,7 +17130,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A140" s="1" t="s">
         <v>708</v>
       </c>
@@ -17127,7 +17171,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A141" s="1" t="s">
         <v>713</v>
       </c>
@@ -17168,7 +17212,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A142" s="1" t="s">
         <v>718</v>
       </c>
@@ -17209,7 +17253,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A143" s="1" t="s">
         <v>723</v>
       </c>
@@ -17250,7 +17294,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A144" s="1" t="s">
         <v>728</v>
       </c>
@@ -17291,7 +17335,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A145" s="1" t="s">
         <v>733</v>
       </c>
@@ -17332,7 +17376,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A146" s="1" t="s">
         <v>738</v>
       </c>
@@ -17373,7 +17417,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A147" s="1" t="s">
         <v>743</v>
       </c>
@@ -17414,7 +17458,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A148" s="1" t="s">
         <v>748</v>
       </c>
@@ -17455,7 +17499,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A149" s="1" t="s">
         <v>753</v>
       </c>
@@ -17496,7 +17540,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A150" s="1" t="s">
         <v>758</v>
       </c>
@@ -17537,7 +17581,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A151" s="1" t="s">
         <v>763</v>
       </c>
@@ -17578,7 +17622,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A152" s="1" t="s">
         <v>768</v>
       </c>
@@ -17619,7 +17663,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A153" s="1" t="s">
         <v>773</v>
       </c>
@@ -17660,7 +17704,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A154" s="1" t="s">
         <v>778</v>
       </c>
@@ -17701,7 +17745,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A155" s="1" t="s">
         <v>783</v>
       </c>
@@ -17742,7 +17786,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A156" s="1" t="s">
         <v>788</v>
       </c>
@@ -17783,7 +17827,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A157" s="1" t="s">
         <v>793</v>
       </c>
@@ -17824,7 +17868,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A158" s="1" t="s">
         <v>798</v>
       </c>
@@ -17865,7 +17909,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A159" s="1" t="s">
         <v>803</v>
       </c>
@@ -17906,7 +17950,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A160" s="1" t="s">
         <v>808</v>
       </c>
@@ -17947,7 +17991,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="161" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A161" s="1" t="s">
         <v>813</v>
       </c>
@@ -17988,7 +18032,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="162" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A162" s="1" t="s">
         <v>818</v>
       </c>
@@ -18029,7 +18073,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="163" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A163" s="1" t="s">
         <v>823</v>
       </c>
@@ -18070,7 +18114,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="164" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A164" s="1" t="s">
         <v>828</v>
       </c>
@@ -18111,7 +18155,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="165" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A165" s="1" t="s">
         <v>833</v>
       </c>
@@ -18152,7 +18196,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="166" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A166" s="1" t="s">
         <v>838</v>
       </c>
@@ -18193,7 +18237,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="167" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A167" s="1" t="s">
         <v>843</v>
       </c>
@@ -18234,7 +18278,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="168" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A168" s="1" t="s">
         <v>848</v>
       </c>
@@ -18275,7 +18319,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="169" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A169" s="1" t="s">
         <v>853</v>
       </c>
@@ -18316,7 +18360,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="170" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A170" s="1" t="s">
         <v>858</v>
       </c>
@@ -18357,7 +18401,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="171" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A171" s="1" t="s">
         <v>863</v>
       </c>
@@ -18398,7 +18442,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="172" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A172" s="1" t="s">
         <v>868</v>
       </c>
@@ -18439,7 +18483,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="173" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A173" s="1" t="s">
         <v>873</v>
       </c>
@@ -18480,7 +18524,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="174" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A174" s="1" t="s">
         <v>878</v>
       </c>
@@ -18521,7 +18565,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="175" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A175" s="1" t="s">
         <v>883</v>
       </c>
@@ -18562,7 +18606,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="176" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A176" s="1" t="s">
         <v>888</v>
       </c>
@@ -18603,7 +18647,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A177" s="1" t="s">
         <v>893</v>
       </c>
@@ -18644,7 +18688,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="178" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A178" s="1" t="s">
         <v>898</v>
       </c>
@@ -18685,7 +18729,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="179" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A179" s="1" t="s">
         <v>903</v>
       </c>
@@ -18726,7 +18770,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A180" s="1" t="s">
         <v>908</v>
       </c>
@@ -18767,7 +18811,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="181" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A181" s="1" t="s">
         <v>913</v>
       </c>
@@ -18808,7 +18852,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="182" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A182" s="1" t="s">
         <v>918</v>
       </c>
@@ -18849,7 +18893,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="183" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A183" s="1" t="s">
         <v>923</v>
       </c>
@@ -18890,7 +18934,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="184" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A184" s="1" t="s">
         <v>928</v>
       </c>
@@ -18931,7 +18975,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="185" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A185" s="1" t="s">
         <v>933</v>
       </c>
@@ -18972,7 +19016,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="186" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A186" s="1" t="s">
         <v>938</v>
       </c>
@@ -19013,7 +19057,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="187" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A187" s="1" t="s">
         <v>943</v>
       </c>
@@ -19054,7 +19098,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="188" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A188" s="1" t="s">
         <v>948</v>
       </c>
@@ -19095,7 +19139,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="189" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A189" s="1" t="s">
         <v>953</v>
       </c>
@@ -19136,7 +19180,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="190" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A190" s="1" t="s">
         <v>958</v>
       </c>
@@ -19177,7 +19221,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="191" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A191" s="1" t="s">
         <v>963</v>
       </c>
@@ -19218,7 +19262,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="192" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A192" s="1" t="s">
         <v>968</v>
       </c>
@@ -19259,7 +19303,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="193" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A193" s="1" t="s">
         <v>973</v>
       </c>
@@ -19300,7 +19344,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="194" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A194" s="1" t="s">
         <v>978</v>
       </c>
@@ -19341,7 +19385,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="195" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A195" s="1" t="s">
         <v>983</v>
       </c>
@@ -19382,7 +19426,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="196" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A196" s="1" t="s">
         <v>988</v>
       </c>
@@ -19423,7 +19467,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="197" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A197" s="1" t="s">
         <v>993</v>
       </c>
@@ -19464,7 +19508,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="198" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A198" s="1" t="s">
         <v>998</v>
       </c>
@@ -19505,7 +19549,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="199" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A199" s="1" t="s">
         <v>1003</v>
       </c>
@@ -19546,7 +19590,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="200" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A200" s="1" t="s">
         <v>1008</v>
       </c>
@@ -19587,7 +19631,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="201" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A201" s="1" t="s">
         <v>1013</v>
       </c>
@@ -19628,7 +19672,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="202" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A202" s="1" t="s">
         <v>1018</v>
       </c>
@@ -19669,7 +19713,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="203" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A203" s="1" t="s">
         <v>1023</v>
       </c>
@@ -19710,7 +19754,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="204" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A204" s="1" t="s">
         <v>1028</v>
       </c>
@@ -19751,7 +19795,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="205" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A205" s="1" t="s">
         <v>1033</v>
       </c>
@@ -19792,7 +19836,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="206" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A206" s="1" t="s">
         <v>1038</v>
       </c>
@@ -19833,7 +19877,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="207" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A207" s="1" t="s">
         <v>1043</v>
       </c>
@@ -19874,7 +19918,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="208" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A208" s="1" t="s">
         <v>1048</v>
       </c>
@@ -19915,7 +19959,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="209" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A209" s="1" t="s">
         <v>1053</v>
       </c>
@@ -19956,7 +20000,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="210" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A210" s="1" t="s">
         <v>1058</v>
       </c>
@@ -19997,7 +20041,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="211" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A211" s="1" t="s">
         <v>1063</v>
       </c>
@@ -20038,7 +20082,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="212" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A212" s="1" t="s">
         <v>1068</v>
       </c>
@@ -20079,7 +20123,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="213" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A213" s="1" t="s">
         <v>1073</v>
       </c>
@@ -20120,7 +20164,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="214" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A214" s="1" t="s">
         <v>1078</v>
       </c>
@@ -20161,7 +20205,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="215" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A215" s="1" t="s">
         <v>1083</v>
       </c>
@@ -20202,7 +20246,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="216" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A216" s="1" t="s">
         <v>1088</v>
       </c>
@@ -20243,7 +20287,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="217" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A217" s="1" t="s">
         <v>1093</v>
       </c>
@@ -20284,7 +20328,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="218" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A218" s="1" t="s">
         <v>1098</v>
       </c>
@@ -20325,7 +20369,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="219" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A219" s="1" t="s">
         <v>1103</v>
       </c>
@@ -20366,7 +20410,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="220" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A220" s="1" t="s">
         <v>1108</v>
       </c>
@@ -20407,7 +20451,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="221" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A221" s="1" t="s">
         <v>1113</v>
       </c>
@@ -20448,7 +20492,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="222" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A222" s="1" t="s">
         <v>1118</v>
       </c>
@@ -20489,7 +20533,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="223" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A223" s="1" t="s">
         <v>1123</v>
       </c>
@@ -20530,7 +20574,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="224" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A224" s="1" t="s">
         <v>1128</v>
       </c>
@@ -20571,7 +20615,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="225" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A225" s="1" t="s">
         <v>1133</v>
       </c>
@@ -20612,7 +20656,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="226" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A226" s="1" t="s">
         <v>1138</v>
       </c>
@@ -20653,7 +20697,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="227" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A227" s="1" t="s">
         <v>1143</v>
       </c>
@@ -20694,7 +20738,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="228" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A228" s="1" t="s">
         <v>1148</v>
       </c>
@@ -20735,7 +20779,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="229" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A229" s="1" t="s">
         <v>1153</v>
       </c>
@@ -20776,7 +20820,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="230" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A230" s="1" t="s">
         <v>1158</v>
       </c>
@@ -20817,7 +20861,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="231" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A231" s="1" t="s">
         <v>1163</v>
       </c>
@@ -20858,7 +20902,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="232" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A232" s="1" t="s">
         <v>1168</v>
       </c>
@@ -20899,7 +20943,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="233" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A233" s="1" t="s">
         <v>1173</v>
       </c>
@@ -20940,7 +20984,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="234" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A234" s="1" t="s">
         <v>1178</v>
       </c>
@@ -20981,7 +21025,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="235" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A235" s="1" t="s">
         <v>1183</v>
       </c>
@@ -21022,7 +21066,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="236" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A236" s="1" t="s">
         <v>1188</v>
       </c>
@@ -21063,7 +21107,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="237" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A237" s="1" t="s">
         <v>1193</v>
       </c>
@@ -21104,7 +21148,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="238" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A238" s="1" t="s">
         <v>1198</v>
       </c>
@@ -21145,7 +21189,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="239" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A239" s="1" t="s">
         <v>1203</v>
       </c>
@@ -21186,7 +21230,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="240" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A240" s="1" t="s">
         <v>1208</v>
       </c>
@@ -21227,7 +21271,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="241" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A241" s="1" t="s">
         <v>1213</v>
       </c>
@@ -21268,7 +21312,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="242" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A242" s="1" t="s">
         <v>1218</v>
       </c>
@@ -21309,7 +21353,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="243" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A243" s="1" t="s">
         <v>1223</v>
       </c>
@@ -21350,7 +21394,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="244" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A244" s="1" t="s">
         <v>1228</v>
       </c>
@@ -21391,7 +21435,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="245" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A245" s="1" t="s">
         <v>1233</v>
       </c>
@@ -21432,7 +21476,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="246" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A246" s="1" t="s">
         <v>1238</v>
       </c>
@@ -21473,7 +21517,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="247" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A247" s="1" t="s">
         <v>1243</v>
       </c>
@@ -21514,7 +21558,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="248" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A248" s="1" t="s">
         <v>1248</v>
       </c>
@@ -21555,7 +21599,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="249" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A249" s="1" t="s">
         <v>1253</v>
       </c>
@@ -21596,7 +21640,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="250" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A250" s="1" t="s">
         <v>1258</v>
       </c>
@@ -21637,7 +21681,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="251" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A251" s="1" t="s">
         <v>1263</v>
       </c>
@@ -21678,7 +21722,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="252" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A252" s="1" t="s">
         <v>1268</v>
       </c>
@@ -21719,7 +21763,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="253" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A253" s="1" t="s">
         <v>1273</v>
       </c>
@@ -21760,7 +21804,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="254" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A254" s="1" t="s">
         <v>1278</v>
       </c>
@@ -21801,7 +21845,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="255" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A255" s="1" t="s">
         <v>1283</v>
       </c>
@@ -21842,7 +21886,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="256" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A256" s="1" t="s">
         <v>1288</v>
       </c>
@@ -21883,7 +21927,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="257" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A257" s="1" t="s">
         <v>1293</v>
       </c>
@@ -21924,7 +21968,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="258" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A258" s="1" t="s">
         <v>1298</v>
       </c>
@@ -21965,7 +22009,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="259" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A259" s="1" t="s">
         <v>1303</v>
       </c>
@@ -22006,7 +22050,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="260" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A260" s="1" t="s">
         <v>1308</v>
       </c>
@@ -22047,7 +22091,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="261" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A261" s="1" t="s">
         <v>1313</v>
       </c>
@@ -22088,7 +22132,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="262" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A262" s="1" t="s">
         <v>1318</v>
       </c>
@@ -22129,7 +22173,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="263" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A263" s="1" t="s">
         <v>1323</v>
       </c>
@@ -22170,7 +22214,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="264" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A264" s="1" t="s">
         <v>1328</v>
       </c>
@@ -22211,7 +22255,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="265" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A265" s="1" t="s">
         <v>1333</v>
       </c>
@@ -22252,7 +22296,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="266" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A266" s="1" t="s">
         <v>1338</v>
       </c>
@@ -22293,7 +22337,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="267" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A267" s="1" t="s">
         <v>1343</v>
       </c>
@@ -22334,7 +22378,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="268" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A268" s="1" t="s">
         <v>1348</v>
       </c>
@@ -22375,7 +22419,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="269" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A269" s="1" t="s">
         <v>1353</v>
       </c>
@@ -22416,7 +22460,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="270" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A270" s="1" t="s">
         <v>1358</v>
       </c>
@@ -22457,7 +22501,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="271" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A271" s="1" t="s">
         <v>1363</v>
       </c>
@@ -22498,7 +22542,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="272" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A272" s="1" t="s">
         <v>1368</v>
       </c>
@@ -22539,7 +22583,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="273" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A273" s="1" t="s">
         <v>1373</v>
       </c>
@@ -22580,7 +22624,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="274" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A274" s="1" t="s">
         <v>1378</v>
       </c>
@@ -22621,7 +22665,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="275" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A275" s="1" t="s">
         <v>1383</v>
       </c>
@@ -22662,7 +22706,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="276" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A276" s="1" t="s">
         <v>1388</v>
       </c>
@@ -22703,7 +22747,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="277" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A277" s="1" t="s">
         <v>1393</v>
       </c>
@@ -22744,7 +22788,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="278" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A278" s="1" t="s">
         <v>1398</v>
       </c>
@@ -22785,7 +22829,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="279" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A279" s="1" t="s">
         <v>1403</v>
       </c>
@@ -22826,7 +22870,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="280" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A280" s="1" t="s">
         <v>1408</v>
       </c>
@@ -22867,7 +22911,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="281" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A281" s="1" t="s">
         <v>1413</v>
       </c>
@@ -22908,7 +22952,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="282" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A282" s="1" t="s">
         <v>1418</v>
       </c>
@@ -22949,7 +22993,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="283" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A283" s="1" t="s">
         <v>1423</v>
       </c>
@@ -22990,7 +23034,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="284" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A284" s="1" t="s">
         <v>1428</v>
       </c>
@@ -23031,7 +23075,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="285" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A285" s="1" t="s">
         <v>1433</v>
       </c>
@@ -23072,7 +23116,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="286" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A286" s="1" t="s">
         <v>1438</v>
       </c>
@@ -23113,7 +23157,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="287" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A287" s="1" t="s">
         <v>1443</v>
       </c>
@@ -23154,7 +23198,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="288" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A288" s="1" t="s">
         <v>1448</v>
       </c>
@@ -23195,7 +23239,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="289" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A289" s="1" t="s">
         <v>1453</v>
       </c>
@@ -23236,7 +23280,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="290" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A290" s="1" t="s">
         <v>1458</v>
       </c>
@@ -23277,7 +23321,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="291" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A291" s="1" t="s">
         <v>1463</v>
       </c>
@@ -23318,7 +23362,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="292" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A292" s="1" t="s">
         <v>1468</v>
       </c>
@@ -23359,7 +23403,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="293" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A293" s="1" t="s">
         <v>1473</v>
       </c>
@@ -23400,7 +23444,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="294" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A294" s="1" t="s">
         <v>1478</v>
       </c>
@@ -23441,7 +23485,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="295" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A295" s="1" t="s">
         <v>1483</v>
       </c>
@@ -23482,7 +23526,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="296" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A296" s="1" t="s">
         <v>1488</v>
       </c>
@@ -23523,7 +23567,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="297" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A297" s="1" t="s">
         <v>1493</v>
       </c>
@@ -23564,7 +23608,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="298" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A298" s="1" t="s">
         <v>1498</v>
       </c>
@@ -23605,7 +23649,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="299" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A299" s="1" t="s">
         <v>1503</v>
       </c>
@@ -23646,7 +23690,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="300" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A300" s="1" t="s">
         <v>1508</v>
       </c>
@@ -23687,7 +23731,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="301" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A301" s="1" t="s">
         <v>1513</v>
       </c>
@@ -23728,7 +23772,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="302" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A302" s="1" t="s">
         <v>1518</v>
       </c>
@@ -23769,7 +23813,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="303" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A303" s="1" t="s">
         <v>1523</v>
       </c>
@@ -23810,7 +23854,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="304" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A304" s="1" t="s">
         <v>1528</v>
       </c>
@@ -23851,7 +23895,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="305" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A305" s="1" t="s">
         <v>1533</v>
       </c>
@@ -23892,7 +23936,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="306" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A306" s="1" t="s">
         <v>1538</v>
       </c>
@@ -23933,7 +23977,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="307" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A307" s="1" t="s">
         <v>1543</v>
       </c>
@@ -23974,7 +24018,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="308" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A308" s="1" t="s">
         <v>1548</v>
       </c>
@@ -24015,7 +24059,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="309" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A309" s="1" t="s">
         <v>1553</v>
       </c>
@@ -24056,7 +24100,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="310" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A310" s="1" t="s">
         <v>1558</v>
       </c>
@@ -24097,7 +24141,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="311" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A311" s="1" t="s">
         <v>1563</v>
       </c>
@@ -24138,7 +24182,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="312" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A312" s="1" t="s">
         <v>1568</v>
       </c>
@@ -24179,7 +24223,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="313" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A313" s="1" t="s">
         <v>1573</v>
       </c>
@@ -24220,7 +24264,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="314" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A314" s="1" t="s">
         <v>1578</v>
       </c>
@@ -24261,7 +24305,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="315" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A315" s="1" t="s">
         <v>1583</v>
       </c>
@@ -24302,7 +24346,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="316" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A316" s="1" t="s">
         <v>1588</v>
       </c>
@@ -24343,7 +24387,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="317" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A317" s="1" t="s">
         <v>1593</v>
       </c>
@@ -24384,7 +24428,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="318" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A318" s="1" t="s">
         <v>1598</v>
       </c>
@@ -24425,7 +24469,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="319" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A319" s="1" t="s">
         <v>1603</v>
       </c>
@@ -24466,7 +24510,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="320" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A320" s="1" t="s">
         <v>1608</v>
       </c>
@@ -24507,7 +24551,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="321" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A321" s="1" t="s">
         <v>1613</v>
       </c>
@@ -24548,7 +24592,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="322" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A322" s="1" t="s">
         <v>1618</v>
       </c>
@@ -24589,7 +24633,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="323" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A323" s="1" t="s">
         <v>1623</v>
       </c>
@@ -24630,7 +24674,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="324" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A324" s="1" t="s">
         <v>1628</v>
       </c>
@@ -24671,7 +24715,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="325" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A325" s="1" t="s">
         <v>1633</v>
       </c>
@@ -24712,7 +24756,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="326" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A326" s="1" t="s">
         <v>1638</v>
       </c>
@@ -24753,7 +24797,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="327" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A327" s="1" t="s">
         <v>1643</v>
       </c>
@@ -24794,7 +24838,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="328" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A328" s="1" t="s">
         <v>1648</v>
       </c>
@@ -24835,7 +24879,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="329" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A329" s="1" t="s">
         <v>1653</v>
       </c>
@@ -24876,7 +24920,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="330" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A330" s="1" t="s">
         <v>1658</v>
       </c>
@@ -24917,7 +24961,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="331" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A331" s="1" t="s">
         <v>1663</v>
       </c>
@@ -24958,7 +25002,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="332" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A332" s="1" t="s">
         <v>1668</v>
       </c>
@@ -24999,7 +25043,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="333" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A333" s="1" t="s">
         <v>1673</v>
       </c>
@@ -25040,7 +25084,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="334" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A334" s="1" t="s">
         <v>1678</v>
       </c>
@@ -25081,7 +25125,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="335" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A335" s="1" t="s">
         <v>1683</v>
       </c>
@@ -25122,7 +25166,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="336" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A336" s="1" t="s">
         <v>1688</v>
       </c>
@@ -25163,7 +25207,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="337" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A337" s="1" t="s">
         <v>1693</v>
       </c>
@@ -25204,7 +25248,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="338" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A338" s="1" t="s">
         <v>1698</v>
       </c>
@@ -25245,7 +25289,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="339" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A339" s="1" t="s">
         <v>1703</v>
       </c>
@@ -25286,7 +25330,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="340" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A340" s="1" t="s">
         <v>1708</v>
       </c>
@@ -25327,7 +25371,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="341" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A341" s="1" t="s">
         <v>1713</v>
       </c>
@@ -25368,7 +25412,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="342" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A342" s="1" t="s">
         <v>1718</v>
       </c>
@@ -25409,7 +25453,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="343" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A343" s="1" t="s">
         <v>1723</v>
       </c>
@@ -25450,7 +25494,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="344" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A344" s="1" t="s">
         <v>1728</v>
       </c>
@@ -25491,7 +25535,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="345" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A345" s="1" t="s">
         <v>1733</v>
       </c>
@@ -25532,7 +25576,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="346" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A346" s="1" t="s">
         <v>1738</v>
       </c>
@@ -25573,7 +25617,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="347" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A347" s="1" t="s">
         <v>1743</v>
       </c>
@@ -25614,7 +25658,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="348" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A348" s="1" t="s">
         <v>1748</v>
       </c>
@@ -25655,7 +25699,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="349" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A349" s="1" t="s">
         <v>1753</v>
       </c>
@@ -25696,7 +25740,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="350" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A350" s="1" t="s">
         <v>1758</v>
       </c>
@@ -25737,7 +25781,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="351" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A351" s="1" t="s">
         <v>1763</v>
       </c>
@@ -25778,7 +25822,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="352" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A352" s="1" t="s">
         <v>1768</v>
       </c>
@@ -25819,7 +25863,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="353" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A353" s="1" t="s">
         <v>1773</v>
       </c>
@@ -25860,7 +25904,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="354" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A354" s="1" t="s">
         <v>1778</v>
       </c>
@@ -25901,7 +25945,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="355" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A355" s="1" t="s">
         <v>1783</v>
       </c>
@@ -25942,7 +25986,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="356" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A356" s="1" t="s">
         <v>1788</v>
       </c>
@@ -25983,7 +26027,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="357" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A357" s="1" t="s">
         <v>1793</v>
       </c>
@@ -26024,7 +26068,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="358" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A358" s="1" t="s">
         <v>1798</v>
       </c>
@@ -26065,7 +26109,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="359" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A359" s="1" t="s">
         <v>1803</v>
       </c>
@@ -26106,7 +26150,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="360" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A360" s="1" t="s">
         <v>1808</v>
       </c>
@@ -26147,7 +26191,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="361" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A361" s="1" t="s">
         <v>1813</v>
       </c>
@@ -26188,7 +26232,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="362" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A362" s="1" t="s">
         <v>1818</v>
       </c>
@@ -26229,7 +26273,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="363" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A363" s="1" t="s">
         <v>1823</v>
       </c>
@@ -26270,7 +26314,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="364" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A364" s="1" t="s">
         <v>1828</v>
       </c>
@@ -26311,7 +26355,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="365" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A365" s="1" t="s">
         <v>1833</v>
       </c>
@@ -26352,7 +26396,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="366" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A366" s="1" t="s">
         <v>1838</v>
       </c>
@@ -26393,7 +26437,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="367" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A367" s="1" t="s">
         <v>1843</v>
       </c>
@@ -26434,7 +26478,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="368" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A368" s="1" t="s">
         <v>1848</v>
       </c>
@@ -26475,7 +26519,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="369" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A369" s="1" t="s">
         <v>1853</v>
       </c>
@@ -26516,7 +26560,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="370" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A370" s="1" t="s">
         <v>1858</v>
       </c>
@@ -26557,7 +26601,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="371" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A371" s="1" t="s">
         <v>1863</v>
       </c>
@@ -26598,7 +26642,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="372" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A372" s="1" t="s">
         <v>1868</v>
       </c>
@@ -26639,7 +26683,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="373" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A373" s="1" t="s">
         <v>1873</v>
       </c>
@@ -26680,7 +26724,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="374" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A374" s="1" t="s">
         <v>1878</v>
       </c>
@@ -26721,7 +26765,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="375" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A375" s="1" t="s">
         <v>1883</v>
       </c>
@@ -26762,7 +26806,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="376" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A376" s="1" t="s">
         <v>1888</v>
       </c>
@@ -26803,7 +26847,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="377" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A377" s="1" t="s">
         <v>1893</v>
       </c>
@@ -26844,7 +26888,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="378" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A378" s="1" t="s">
         <v>1898</v>
       </c>
@@ -26885,7 +26929,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="379" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A379" s="1" t="s">
         <v>1903</v>
       </c>
@@ -26926,7 +26970,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="380" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A380" s="1" t="s">
         <v>1908</v>
       </c>
@@ -26967,7 +27011,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="381" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A381" s="1" t="s">
         <v>1913</v>
       </c>
@@ -27008,7 +27052,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="382" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A382" s="1" t="s">
         <v>1918</v>
       </c>
@@ -27049,7 +27093,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="383" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A383" s="1" t="s">
         <v>1923</v>
       </c>
@@ -27090,7 +27134,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="384" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A384" s="1" t="s">
         <v>1928</v>
       </c>
@@ -27131,7 +27175,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="385" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A385" s="1" t="s">
         <v>1933</v>
       </c>
@@ -27172,7 +27216,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="386" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A386" s="1" t="s">
         <v>1938</v>
       </c>
@@ -27213,7 +27257,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="387" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A387" s="1" t="s">
         <v>1943</v>
       </c>
@@ -27254,7 +27298,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="388" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A388" s="1" t="s">
         <v>1948</v>
       </c>
@@ -27295,7 +27339,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="389" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A389" s="1" t="s">
         <v>1953</v>
       </c>
@@ -27336,7 +27380,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="390" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A390" s="1" t="s">
         <v>1958</v>
       </c>
@@ -27377,7 +27421,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="391" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A391" s="1" t="s">
         <v>1963</v>
       </c>
@@ -27418,7 +27462,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="392" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A392" s="1" t="s">
         <v>1968</v>
       </c>
@@ -27459,7 +27503,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="393" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A393" s="1" t="s">
         <v>1973</v>
       </c>
@@ -27500,7 +27544,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="394" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A394" s="1" t="s">
         <v>1978</v>
       </c>
@@ -27541,7 +27585,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="395" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A395" s="1" t="s">
         <v>1983</v>
       </c>
@@ -27582,7 +27626,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="396" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A396" s="1" t="s">
         <v>1988</v>
       </c>
@@ -27623,7 +27667,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="397" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A397" s="1" t="s">
         <v>1993</v>
       </c>
@@ -27664,7 +27708,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="398" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A398" s="1" t="s">
         <v>1998</v>
       </c>
@@ -27705,7 +27749,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="399" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A399" s="1" t="s">
         <v>2003</v>
       </c>
@@ -27746,7 +27790,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="400" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A400" s="1" t="s">
         <v>2008</v>
       </c>
@@ -27787,7 +27831,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="401" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A401" s="1" t="s">
         <v>2013</v>
       </c>
@@ -27828,7 +27872,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="402" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A402" s="1" t="s">
         <v>2018</v>
       </c>
@@ -27869,7 +27913,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="403" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A403" s="1" t="s">
         <v>2023</v>
       </c>
@@ -27910,7 +27954,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="404" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A404" s="1" t="s">
         <v>2028</v>
       </c>
@@ -27951,7 +27995,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="405" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A405" s="1" t="s">
         <v>2033</v>
       </c>
@@ -27992,7 +28036,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="406" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A406" s="1" t="s">
         <v>2038</v>
       </c>
@@ -28033,7 +28077,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="407" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A407" s="1" t="s">
         <v>2043</v>
       </c>
@@ -28074,7 +28118,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="408" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A408" s="1" t="s">
         <v>2048</v>
       </c>
@@ -28115,7 +28159,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="409" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A409" s="1" t="s">
         <v>2053</v>
       </c>
@@ -28156,7 +28200,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="410" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A410" s="1" t="s">
         <v>2058</v>
       </c>
@@ -28197,7 +28241,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="411" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A411" s="1" t="s">
         <v>2063</v>
       </c>
@@ -28238,7 +28282,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="412" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A412" s="1" t="s">
         <v>2068</v>
       </c>
@@ -28279,7 +28323,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="413" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A413" s="1" t="s">
         <v>2073</v>
       </c>
@@ -28320,7 +28364,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="414" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A414" s="1" t="s">
         <v>2078</v>
       </c>
@@ -28361,7 +28405,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="415" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A415" s="1" t="s">
         <v>2083</v>
       </c>
@@ -28402,7 +28446,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="416" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A416" s="1" t="s">
         <v>2088</v>
       </c>
@@ -28443,7 +28487,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="417" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A417" s="1" t="s">
         <v>2093</v>
       </c>
@@ -28484,7 +28528,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="418" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A418" s="1" t="s">
         <v>2098</v>
       </c>
@@ -28525,7 +28569,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="419" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A419" s="1" t="s">
         <v>2103</v>
       </c>
@@ -28566,7 +28610,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="420" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A420" s="1" t="s">
         <v>2108</v>
       </c>
@@ -28607,7 +28651,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="421" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A421" s="1" t="s">
         <v>2113</v>
       </c>
@@ -28648,7 +28692,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="422" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A422" s="1" t="s">
         <v>2118</v>
       </c>
@@ -28689,7 +28733,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="423" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A423" s="1" t="s">
         <v>2123</v>
       </c>
@@ -28730,7 +28774,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="424" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A424" s="1" t="s">
         <v>2128</v>
       </c>
@@ -28771,7 +28815,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="425" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A425" s="1" t="s">
         <v>2133</v>
       </c>
@@ -28812,7 +28856,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="426" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A426" s="1" t="s">
         <v>2138</v>
       </c>
@@ -28853,7 +28897,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="427" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A427" s="1" t="s">
         <v>2143</v>
       </c>
@@ -28894,7 +28938,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="428" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A428" s="1" t="s">
         <v>2148</v>
       </c>
@@ -28935,7 +28979,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="429" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A429" s="1" t="s">
         <v>2153</v>
       </c>
@@ -28976,7 +29020,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="430" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A430" s="1" t="s">
         <v>2158</v>
       </c>
@@ -29017,7 +29061,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="431" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A431" s="1" t="s">
         <v>2163</v>
       </c>
@@ -29058,7 +29102,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="432" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A432" s="1" t="s">
         <v>2168</v>
       </c>
@@ -29099,7 +29143,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="433" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A433" s="1" t="s">
         <v>2173</v>
       </c>
@@ -29140,7 +29184,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="434" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A434" s="1" t="s">
         <v>2178</v>
       </c>
@@ -29181,7 +29225,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="435" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A435" s="1" t="s">
         <v>2183</v>
       </c>
@@ -29222,7 +29266,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="436" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A436" s="1" t="s">
         <v>2188</v>
       </c>
@@ -29263,7 +29307,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="437" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A437" s="1" t="s">
         <v>2193</v>
       </c>
@@ -29304,7 +29348,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="438" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A438" s="1" t="s">
         <v>2198</v>
       </c>
@@ -29345,7 +29389,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="439" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A439" s="1" t="s">
         <v>2203</v>
       </c>
@@ -29386,7 +29430,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="440" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A440" s="1" t="s">
         <v>2208</v>
       </c>
@@ -29427,7 +29471,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="441" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A441" s="1" t="s">
         <v>2213</v>
       </c>
@@ -29468,7 +29512,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="442" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A442" s="1" t="s">
         <v>2218</v>
       </c>
@@ -29509,7 +29553,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="443" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A443" s="1" t="s">
         <v>2223</v>
       </c>
@@ -29550,7 +29594,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="444" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A444" s="1" t="s">
         <v>2228</v>
       </c>
@@ -29591,7 +29635,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="445" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A445" s="1" t="s">
         <v>2233</v>
       </c>
@@ -29632,7 +29676,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="446" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A446" s="1" t="s">
         <v>2238</v>
       </c>
@@ -29673,7 +29717,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="447" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A447" s="1" t="s">
         <v>2243</v>
       </c>
@@ -29714,7 +29758,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="448" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A448" s="1" t="s">
         <v>2248</v>
       </c>
@@ -29755,7 +29799,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="449" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A449" s="1" t="s">
         <v>2253</v>
       </c>
@@ -29796,7 +29840,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="450" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A450" s="1" t="s">
         <v>2258</v>
       </c>
@@ -29837,7 +29881,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="451" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A451" s="1" t="s">
         <v>2263</v>
       </c>
@@ -29878,7 +29922,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="452" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A452" s="1" t="s">
         <v>2268</v>
       </c>
@@ -29919,7 +29963,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="453" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A453" s="1" t="s">
         <v>2273</v>
       </c>
@@ -29960,7 +30004,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="454" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A454" s="1" t="s">
         <v>2278</v>
       </c>
@@ -30001,7 +30045,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="455" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A455" s="1" t="s">
         <v>2281</v>
       </c>
@@ -30042,7 +30086,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="456" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A456" s="1" t="s">
         <v>2286</v>
       </c>
@@ -30083,7 +30127,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="457" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A457" s="1" t="s">
         <v>2291</v>
       </c>
@@ -30124,7 +30168,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="458" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A458" s="1" t="s">
         <v>2296</v>
       </c>
@@ -30165,7 +30209,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="459" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A459" s="1" t="s">
         <v>2301</v>
       </c>
@@ -30206,7 +30250,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="460" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A460" s="1" t="s">
         <v>2306</v>
       </c>
@@ -30247,7 +30291,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="461" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A461" s="1" t="s">
         <v>2311</v>
       </c>
@@ -30288,7 +30332,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="462" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A462" s="1" t="s">
         <v>2316</v>
       </c>
@@ -30329,7 +30373,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="463" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A463" s="1" t="s">
         <v>2321</v>
       </c>
@@ -30370,7 +30414,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="464" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A464" s="1" t="s">
         <v>2326</v>
       </c>
@@ -30411,7 +30455,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="465" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A465" s="1" t="s">
         <v>2331</v>
       </c>
@@ -30452,7 +30496,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="466" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A466" s="1" t="s">
         <v>2334</v>
       </c>
@@ -30493,7 +30537,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="467" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A467" s="1" t="s">
         <v>2337</v>
       </c>
@@ -30534,7 +30578,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="468" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A468" s="1" t="s">
         <v>2342</v>
       </c>
@@ -30575,7 +30619,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="469" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A469" s="1" t="s">
         <v>2347</v>
       </c>
@@ -30616,7 +30660,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="470" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A470" s="1" t="s">
         <v>2352</v>
       </c>
@@ -30657,7 +30701,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="471" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A471" s="1" t="s">
         <v>2357</v>
       </c>
@@ -30698,7 +30742,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="472" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A472" s="1" t="s">
         <v>2362</v>
       </c>
@@ -30739,7 +30783,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="473" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A473" s="1" t="s">
         <v>2367</v>
       </c>
@@ -30780,7 +30824,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="474" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A474" s="1" t="s">
         <v>2372</v>
       </c>
@@ -30821,7 +30865,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="475" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A475" s="1" t="s">
         <v>2377</v>
       </c>
@@ -30862,7 +30906,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="476" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A476" s="1" t="s">
         <v>2382</v>
       </c>
@@ -30903,7 +30947,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="477" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A477" s="1" t="s">
         <v>2387</v>
       </c>
@@ -30944,7 +30988,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="478" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A478" s="1" t="s">
         <v>2392</v>
       </c>
@@ -30985,7 +31029,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="479" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A479" s="1" t="s">
         <v>2397</v>
       </c>
@@ -31026,7 +31070,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="480" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A480" s="1" t="s">
         <v>2402</v>
       </c>
@@ -31067,7 +31111,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="481" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A481" s="1" t="s">
         <v>2407</v>
       </c>
@@ -31108,7 +31152,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="482" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A482" s="1" t="s">
         <v>2412</v>
       </c>
@@ -31149,7 +31193,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="483" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A483" s="1" t="s">
         <v>2417</v>
       </c>
@@ -31190,7 +31234,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="484" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A484" s="1" t="s">
         <v>2422</v>
       </c>
@@ -31231,7 +31275,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="485" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A485" s="1" t="s">
         <v>2427</v>
       </c>
@@ -31272,7 +31316,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="486" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A486" s="1" t="s">
         <v>2432</v>
       </c>
@@ -31313,7 +31357,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="487" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A487" s="1" t="s">
         <v>2437</v>
       </c>
@@ -31354,7 +31398,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="488" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A488" s="1" t="s">
         <v>2442</v>
       </c>
@@ -31395,7 +31439,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="489" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A489" s="1" t="s">
         <v>2447</v>
       </c>
@@ -31436,7 +31480,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="490" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A490" s="1" t="s">
         <v>2452</v>
       </c>
@@ -31477,7 +31521,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="491" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A491" s="1" t="s">
         <v>2457</v>
       </c>
@@ -31518,7 +31562,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="492" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A492" s="1" t="s">
         <v>2462</v>
       </c>
@@ -31559,7 +31603,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="493" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A493" s="1" t="s">
         <v>2467</v>
       </c>
@@ -31600,7 +31644,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="494" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A494" s="1" t="s">
         <v>2472</v>
       </c>
@@ -31641,7 +31685,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="495" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A495" s="1" t="s">
         <v>2477</v>
       </c>
@@ -31682,7 +31726,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="496" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A496" s="1" t="s">
         <v>2482</v>
       </c>
@@ -31723,7 +31767,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="497" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A497" s="1" t="s">
         <v>2487</v>
       </c>
@@ -31764,7 +31808,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="498" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A498" s="1" t="s">
         <v>2492</v>
       </c>
@@ -31805,7 +31849,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="499" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A499" s="1" t="s">
         <v>2497</v>
       </c>
@@ -31846,7 +31890,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="500" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A500" s="1" t="s">
         <v>2502</v>
       </c>
@@ -31887,7 +31931,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="501" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A501" s="1" t="s">
         <v>2507</v>
       </c>
@@ -31928,7 +31972,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="502" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A502" s="1" t="s">
         <v>2512</v>
       </c>
@@ -31969,7 +32013,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="503" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A503" s="1" t="s">
         <v>2517</v>
       </c>
@@ -32010,7 +32054,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="504" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A504" s="1" t="s">
         <v>2522</v>
       </c>
@@ -32051,7 +32095,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="505" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A505" s="1" t="s">
         <v>2527</v>
       </c>
@@ -32092,7 +32136,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="506" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A506" s="1" t="s">
         <v>2532</v>
       </c>
@@ -32133,7 +32177,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="507" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A507" s="1" t="s">
         <v>2537</v>
       </c>
@@ -32174,7 +32218,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="508" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A508" s="1" t="s">
         <v>2542</v>
       </c>
@@ -32215,7 +32259,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="509" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A509" s="1" t="s">
         <v>2547</v>
       </c>
@@ -32256,7 +32300,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="510" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A510" s="1" t="s">
         <v>2552</v>
       </c>
@@ -32297,7 +32341,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="511" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A511" s="1" t="s">
         <v>2557</v>
       </c>
@@ -32338,7 +32382,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="512" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A512" s="1" t="s">
         <v>2562</v>
       </c>
@@ -32379,7 +32423,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="513" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A513" s="1" t="s">
         <v>2567</v>
       </c>
@@ -32420,7 +32464,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="514" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A514" s="1" t="s">
         <v>2572</v>
       </c>
@@ -32461,7 +32505,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="515" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A515" s="1" t="s">
         <v>2577</v>
       </c>
@@ -32502,7 +32546,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="516" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A516" s="1" t="s">
         <v>2582</v>
       </c>
@@ -32543,7 +32587,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="517" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A517" s="1" t="s">
         <v>2587</v>
       </c>
@@ -32584,7 +32628,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="518" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A518" s="1" t="s">
         <v>2592</v>
       </c>
@@ -32625,7 +32669,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="519" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A519" s="1" t="s">
         <v>2597</v>
       </c>
@@ -32666,7 +32710,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="520" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A520" s="1" t="s">
         <v>2602</v>
       </c>
@@ -32707,7 +32751,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="521" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A521" s="1" t="s">
         <v>2607</v>
       </c>
@@ -32748,7 +32792,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="522" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A522" s="1" t="s">
         <v>2612</v>
       </c>
@@ -32789,7 +32833,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="523" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A523" s="1" t="s">
         <v>2617</v>
       </c>
@@ -32830,7 +32874,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="524" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A524" s="1" t="s">
         <v>2622</v>
       </c>
@@ -32871,7 +32915,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="525" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A525" s="1" t="s">
         <v>2627</v>
       </c>
@@ -32912,7 +32956,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="526" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A526" s="1" t="s">
         <v>2632</v>
       </c>
@@ -32953,7 +32997,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="527" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A527" s="1" t="s">
         <v>2637</v>
       </c>
@@ -32994,7 +33038,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="528" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A528" s="1" t="s">
         <v>2642</v>
       </c>
@@ -33035,7 +33079,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="529" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A529" s="1" t="s">
         <v>2647</v>
       </c>
@@ -33076,7 +33120,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="530" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A530" s="1" t="s">
         <v>2652</v>
       </c>
@@ -33117,7 +33161,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="531" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A531" s="1" t="s">
         <v>2657</v>
       </c>
@@ -33158,7 +33202,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="532" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A532" s="1" t="s">
         <v>2662</v>
       </c>
@@ -33199,7 +33243,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="533" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A533" s="1" t="s">
         <v>2667</v>
       </c>
@@ -33240,7 +33284,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="534" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A534" s="1" t="s">
         <v>2672</v>
       </c>
@@ -33281,7 +33325,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="535" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A535" s="1" t="s">
         <v>2677</v>
       </c>
@@ -33322,7 +33366,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="536" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A536" s="1" t="s">
         <v>2682</v>
       </c>
@@ -33363,7 +33407,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="537" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A537" s="1" t="s">
         <v>2687</v>
       </c>
@@ -33404,7 +33448,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="538" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A538" s="1" t="s">
         <v>2692</v>
       </c>
@@ -33445,7 +33489,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="539" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A539" s="1" t="s">
         <v>2697</v>
       </c>
@@ -33486,7 +33530,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="540" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A540" s="1" t="s">
         <v>2702</v>
       </c>
@@ -33527,7 +33571,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="541" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A541" s="1" t="s">
         <v>2707</v>
       </c>
@@ -33568,7 +33612,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="542" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A542" s="1" t="s">
         <v>2712</v>
       </c>
@@ -33609,7 +33653,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="543" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A543" s="1" t="s">
         <v>2717</v>
       </c>
@@ -33650,7 +33694,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="544" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A544" s="1" t="s">
         <v>2722</v>
       </c>
@@ -33691,7 +33735,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="545" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A545" s="1" t="s">
         <v>2727</v>
       </c>
@@ -33732,7 +33776,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="546" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A546" s="1" t="s">
         <v>2732</v>
       </c>
@@ -33773,7 +33817,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="547" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A547" s="1" t="s">
         <v>2737</v>
       </c>
@@ -33814,7 +33858,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="548" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A548" s="1" t="s">
         <v>2742</v>
       </c>
@@ -33855,7 +33899,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="549" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A549" s="1" t="s">
         <v>2747</v>
       </c>
@@ -33896,7 +33940,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="550" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A550" s="1" t="s">
         <v>2752</v>
       </c>
@@ -33937,7 +33981,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="551" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A551" s="1" t="s">
         <v>2757</v>
       </c>
@@ -33978,7 +34022,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="552" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A552" s="1" t="s">
         <v>2762</v>
       </c>
@@ -34019,7 +34063,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="553" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A553" s="1" t="s">
         <v>2767</v>
       </c>
@@ -34060,7 +34104,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="554" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A554" s="1" t="s">
         <v>2772</v>
       </c>
@@ -34101,7 +34145,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="555" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A555" s="1" t="s">
         <v>2777</v>
       </c>
@@ -34142,7 +34186,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="556" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A556" s="1" t="s">
         <v>2782</v>
       </c>
@@ -34183,7 +34227,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="557" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A557" s="1" t="s">
         <v>2787</v>
       </c>
@@ -34224,7 +34268,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="558" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A558" s="1" t="s">
         <v>2792</v>
       </c>
@@ -34265,7 +34309,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="559" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A559" s="1" t="s">
         <v>2797</v>
       </c>
@@ -34306,7 +34350,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="560" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A560" s="1" t="s">
         <v>2802</v>
       </c>
@@ -34347,7 +34391,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="561" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A561" s="1" t="s">
         <v>2805</v>
       </c>
@@ -34388,7 +34432,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="562" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A562" s="1" t="s">
         <v>2810</v>
       </c>
@@ -34429,7 +34473,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="563" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A563" s="1" t="s">
         <v>2815</v>
       </c>
@@ -34470,7 +34514,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="564" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A564" s="1" t="s">
         <v>2820</v>
       </c>
@@ -34511,7 +34555,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="565" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A565" s="1" t="s">
         <v>2825</v>
       </c>
@@ -34552,7 +34596,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="566" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A566" s="1" t="s">
         <v>2830</v>
       </c>
@@ -34593,7 +34637,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="567" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A567" s="1" t="s">
         <v>2835</v>
       </c>
@@ -34634,7 +34678,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="568" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A568" s="1" t="s">
         <v>2840</v>
       </c>
@@ -34675,7 +34719,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="569" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A569" s="1" t="s">
         <v>2845</v>
       </c>
@@ -34716,7 +34760,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="570" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A570" s="1" t="s">
         <v>2850</v>
       </c>
@@ -34757,7 +34801,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="571" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A571" s="1" t="s">
         <v>2855</v>
       </c>
@@ -34798,7 +34842,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="572" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A572" s="1" t="s">
         <v>2860</v>
       </c>
@@ -34839,7 +34883,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="573" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A573" s="1" t="s">
         <v>2865</v>
       </c>
@@ -34880,7 +34924,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="574" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A574" s="1" t="s">
         <v>2870</v>
       </c>
@@ -34921,7 +34965,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="575" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A575" s="1" t="s">
         <v>2875</v>
       </c>
@@ -34962,7 +35006,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="576" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A576" s="1" t="s">
         <v>2880</v>
       </c>
@@ -35003,7 +35047,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="577" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A577" s="1" t="s">
         <v>2885</v>
       </c>
@@ -35044,7 +35088,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="578" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A578" s="1" t="s">
         <v>2890</v>
       </c>
@@ -35085,7 +35129,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="579" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A579" s="1" t="s">
         <v>2895</v>
       </c>
@@ -35126,7 +35170,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="580" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A580" s="1" t="s">
         <v>2900</v>
       </c>
@@ -35167,7 +35211,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="581" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A581" s="1" t="s">
         <v>2905</v>
       </c>
@@ -35208,7 +35252,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="582" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A582" s="1" t="s">
         <v>2910</v>
       </c>
@@ -35249,7 +35293,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="583" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A583" s="1" t="s">
         <v>2915</v>
       </c>
@@ -35290,7 +35334,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="584" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A584" s="1" t="s">
         <v>2920</v>
       </c>
@@ -35331,7 +35375,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="585" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A585" s="1" t="s">
         <v>2925</v>
       </c>
@@ -35372,7 +35416,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="586" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A586" s="1" t="s">
         <v>2930</v>
       </c>
@@ -35413,7 +35457,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="587" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A587" s="1" t="s">
         <v>2935</v>
       </c>
@@ -35454,7 +35498,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="588" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A588" s="1" t="s">
         <v>2940</v>
       </c>
@@ -35495,7 +35539,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="589" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A589" s="1" t="s">
         <v>2945</v>
       </c>
@@ -35536,7 +35580,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="590" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A590" s="1" t="s">
         <v>2950</v>
       </c>
@@ -35577,7 +35621,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="591" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A591" s="1" t="s">
         <v>2955</v>
       </c>
@@ -35618,7 +35662,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="592" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A592" s="1" t="s">
         <v>2960</v>
       </c>
@@ -35659,7 +35703,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="593" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A593" s="1" t="s">
         <v>2965</v>
       </c>
@@ -35700,7 +35744,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="594" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A594" s="1" t="s">
         <v>2970</v>
       </c>
@@ -35741,7 +35785,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="595" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A595" s="1" t="s">
         <v>2975</v>
       </c>
@@ -35782,7 +35826,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="596" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A596" s="1" t="s">
         <v>2980</v>
       </c>
@@ -35823,7 +35867,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="597" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A597" s="1" t="s">
         <v>2985</v>
       </c>
@@ -35864,7 +35908,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="598" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A598" s="1" t="s">
         <v>2990</v>
       </c>
@@ -35905,7 +35949,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="599" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A599" s="1" t="s">
         <v>2995</v>
       </c>
@@ -35946,7 +35990,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="600" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A600" s="1" t="s">
         <v>3000</v>
       </c>
@@ -35987,7 +36031,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="601" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A601" s="1" t="s">
         <v>3005</v>
       </c>
@@ -36028,7 +36072,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="602" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A602" s="1" t="s">
         <v>3010</v>
       </c>
@@ -36069,7 +36113,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="603" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A603" s="1" t="s">
         <v>3015</v>
       </c>
@@ -36110,7 +36154,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="604" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A604" s="1" t="s">
         <v>3020</v>
       </c>
@@ -36151,7 +36195,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="605" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A605" s="1" t="s">
         <v>3025</v>
       </c>
@@ -36192,7 +36236,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="606" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A606" s="1" t="s">
         <v>3030</v>
       </c>
@@ -36233,7 +36277,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="607" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A607" s="1" t="s">
         <v>3035</v>
       </c>
@@ -36274,7 +36318,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="608" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A608" s="1" t="s">
         <v>3040</v>
       </c>
@@ -36315,7 +36359,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="609" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A609" s="1" t="s">
         <v>3045</v>
       </c>
@@ -36356,7 +36400,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="610" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A610" s="1" t="s">
         <v>3050</v>
       </c>
@@ -36397,7 +36441,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="611" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A611" s="1" t="s">
         <v>3055</v>
       </c>
@@ -36438,7 +36482,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="612" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A612" s="1" t="s">
         <v>3060</v>
       </c>
@@ -36479,7 +36523,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="613" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A613" s="1" t="s">
         <v>3065</v>
       </c>
@@ -36520,7 +36564,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="614" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A614" s="1" t="s">
         <v>3070</v>
       </c>
@@ -36561,7 +36605,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="615" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A615" s="1" t="s">
         <v>3075</v>
       </c>
@@ -36602,7 +36646,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="616" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A616" s="1" t="s">
         <v>3080</v>
       </c>
@@ -36643,7 +36687,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="617" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A617" s="1" t="s">
         <v>3085</v>
       </c>
@@ -36684,7 +36728,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="618" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A618" s="1" t="s">
         <v>3090</v>
       </c>
@@ -36725,7 +36769,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="619" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A619" s="1" t="s">
         <v>3095</v>
       </c>
@@ -36766,7 +36810,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="620" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A620" s="1" t="s">
         <v>3100</v>
       </c>
@@ -36807,7 +36851,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="621" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A621" s="1" t="s">
         <v>3105</v>
       </c>
@@ -36848,7 +36892,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="622" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A622" s="1" t="s">
         <v>3110</v>
       </c>
@@ -36889,7 +36933,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="623" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A623" s="1" t="s">
         <v>3115</v>
       </c>
@@ -36930,7 +36974,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="624" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A624" s="1" t="s">
         <v>3120</v>
       </c>
@@ -36971,7 +37015,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="625" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A625" s="1" t="s">
         <v>3125</v>
       </c>
@@ -37012,7 +37056,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="626" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A626" s="1" t="s">
         <v>3130</v>
       </c>
@@ -37053,7 +37097,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="627" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A627" s="1" t="s">
         <v>3135</v>
       </c>
@@ -37094,7 +37138,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="628" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A628" s="1" t="s">
         <v>3140</v>
       </c>
@@ -37135,7 +37179,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="629" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A629" s="1" t="s">
         <v>3145</v>
       </c>
@@ -37176,7 +37220,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="630" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A630" s="1" t="s">
         <v>3150</v>
       </c>
@@ -37217,7 +37261,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="631" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A631" s="1" t="s">
         <v>3155</v>
       </c>
@@ -37258,7 +37302,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="632" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A632" s="1" t="s">
         <v>3160</v>
       </c>
@@ -37299,7 +37343,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="633" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A633" s="1" t="s">
         <v>3165</v>
       </c>
@@ -37340,7 +37384,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="634" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A634" s="1" t="s">
         <v>3170</v>
       </c>
@@ -37381,7 +37425,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="635" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A635" s="1" t="s">
         <v>3175</v>
       </c>
@@ -37422,7 +37466,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="636" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A636" s="1" t="s">
         <v>3180</v>
       </c>
@@ -37463,7 +37507,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="637" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A637" s="1" t="s">
         <v>3185</v>
       </c>
@@ -37504,7 +37548,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="638" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A638" s="1" t="s">
         <v>3190</v>
       </c>
@@ -37545,7 +37589,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="639" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A639" s="1" t="s">
         <v>3195</v>
       </c>
@@ -37586,7 +37630,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="640" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A640" s="1" t="s">
         <v>3200</v>
       </c>
@@ -37627,7 +37671,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="641" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A641" s="1" t="s">
         <v>3205</v>
       </c>
@@ -37668,7 +37712,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="642" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A642" s="1" t="s">
         <v>3210</v>
       </c>
@@ -37709,7 +37753,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="643" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A643" s="1" t="s">
         <v>3215</v>
       </c>
@@ -37750,7 +37794,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="644" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A644" s="1" t="s">
         <v>3220</v>
       </c>
@@ -37791,7 +37835,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="645" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A645" s="1" t="s">
         <v>3225</v>
       </c>
@@ -37832,7 +37876,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="646" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A646" s="1" t="s">
         <v>3230</v>
       </c>
@@ -37873,7 +37917,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="647" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A647" s="1" t="s">
         <v>3235</v>
       </c>
@@ -37914,7 +37958,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="648" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A648" s="1" t="s">
         <v>3240</v>
       </c>
@@ -37955,7 +37999,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="649" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A649" s="1" t="s">
         <v>3245</v>
       </c>
@@ -37996,7 +38040,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="650" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A650" s="1" t="s">
         <v>3250</v>
       </c>
@@ -38037,7 +38081,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="651" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A651" s="1" t="s">
         <v>3255</v>
       </c>
@@ -38078,7 +38122,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="652" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A652" s="1" t="s">
         <v>3260</v>
       </c>
@@ -38119,7 +38163,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="653" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A653" s="1" t="s">
         <v>3265</v>
       </c>
@@ -38160,7 +38204,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="654" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A654" s="1" t="s">
         <v>3270</v>
       </c>
@@ -38201,7 +38245,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="655" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A655" s="1" t="s">
         <v>3275</v>
       </c>
@@ -38242,7 +38286,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="656" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A656" s="1" t="s">
         <v>3280</v>
       </c>
@@ -38283,7 +38327,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="657" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A657" s="1" t="s">
         <v>3285</v>
       </c>
@@ -38324,7 +38368,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="658" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A658" s="1" t="s">
         <v>3290</v>
       </c>
@@ -38365,7 +38409,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="659" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A659" s="1" t="s">
         <v>3295</v>
       </c>
@@ -38406,7 +38450,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="660" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A660" s="1" t="s">
         <v>3300</v>
       </c>
@@ -38447,7 +38491,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="661" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A661" s="1" t="s">
         <v>3305</v>
       </c>
@@ -38488,7 +38532,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="662" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A662" s="1" t="s">
         <v>3310</v>
       </c>
@@ -38529,7 +38573,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="663" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A663" s="1" t="s">
         <v>3315</v>
       </c>
@@ -38570,7 +38614,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="664" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A664" s="1" t="s">
         <v>3320</v>
       </c>
@@ -38611,7 +38655,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="665" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A665" s="1" t="s">
         <v>3325</v>
       </c>
@@ -38652,7 +38696,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="666" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A666" s="1" t="s">
         <v>3330</v>
       </c>
@@ -38693,7 +38737,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="667" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A667" s="1" t="s">
         <v>3335</v>
       </c>
@@ -38734,7 +38778,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="668" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A668" s="1" t="s">
         <v>3340</v>
       </c>
@@ -38775,7 +38819,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="669" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A669" s="1" t="s">
         <v>3345</v>
       </c>
@@ -38816,7 +38860,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="670" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A670" s="1" t="s">
         <v>3350</v>
       </c>
@@ -38857,7 +38901,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="671" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A671" s="1" t="s">
         <v>3355</v>
       </c>
@@ -38898,7 +38942,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="672" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A672" s="1" t="s">
         <v>3360</v>
       </c>
@@ -38939,7 +38983,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="673" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A673" s="1" t="s">
         <v>3365</v>
       </c>
@@ -38980,7 +39024,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="674" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A674" s="1" t="s">
         <v>3370</v>
       </c>
@@ -39021,7 +39065,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="675" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A675" s="1" t="s">
         <v>3375</v>
       </c>
@@ -39062,7 +39106,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="676" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A676" s="1" t="s">
         <v>3380</v>
       </c>
@@ -39103,7 +39147,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="677" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A677" s="1" t="s">
         <v>3385</v>
       </c>
@@ -39144,7 +39188,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="678" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A678" s="1" t="s">
         <v>3390</v>
       </c>
@@ -39185,7 +39229,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="679" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A679" s="1" t="s">
         <v>3395</v>
       </c>
@@ -39226,7 +39270,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="680" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A680" s="1" t="s">
         <v>3400</v>
       </c>
@@ -39267,7 +39311,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="681" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A681" s="1" t="s">
         <v>3405</v>
       </c>
@@ -39308,7 +39352,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="682" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A682" s="1" t="s">
         <v>3410</v>
       </c>
@@ -39349,7 +39393,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="683" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A683" s="1" t="s">
         <v>3415</v>
       </c>
@@ -39390,7 +39434,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="684" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A684" s="1" t="s">
         <v>3420</v>
       </c>
@@ -39431,7 +39475,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="685" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A685" s="1" t="s">
         <v>3425</v>
       </c>
@@ -39472,7 +39516,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="686" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A686" s="1" t="s">
         <v>3430</v>
       </c>
@@ -39513,7 +39557,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="687" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A687" s="1" t="s">
         <v>3435</v>
       </c>
@@ -39554,7 +39598,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="688" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A688" s="1" t="s">
         <v>3440</v>
       </c>
@@ -39595,7 +39639,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="689" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A689" s="1" t="s">
         <v>3445</v>
       </c>
@@ -39636,7 +39680,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="690" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A690" s="1" t="s">
         <v>3450</v>
       </c>
@@ -39677,7 +39721,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="691" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A691" s="1" t="s">
         <v>3455</v>
       </c>
@@ -39718,7 +39762,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="692" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A692" s="1" t="s">
         <v>3460</v>
       </c>
@@ -39759,7 +39803,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="693" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A693" s="1" t="s">
         <v>3465</v>
       </c>
@@ -39800,7 +39844,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="694" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A694" s="1" t="s">
         <v>3470</v>
       </c>
@@ -39841,7 +39885,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="695" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A695" s="1" t="s">
         <v>3475</v>
       </c>
@@ -39882,7 +39926,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="696" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A696" s="1" t="s">
         <v>3480</v>
       </c>
@@ -39923,7 +39967,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="697" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A697" s="1" t="s">
         <v>3485</v>
       </c>
@@ -39964,7 +40008,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="698" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A698" s="1" t="s">
         <v>3490</v>
       </c>
@@ -40005,7 +40049,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="699" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A699" s="1" t="s">
         <v>3495</v>
       </c>
@@ -40046,7 +40090,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="700" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A700" s="1" t="s">
         <v>3500</v>
       </c>
@@ -40087,7 +40131,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="701" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A701" s="1" t="s">
         <v>3505</v>
       </c>
@@ -40128,7 +40172,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="702" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A702" s="1" t="s">
         <v>3510</v>
       </c>
@@ -40169,7 +40213,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="703" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A703" s="1" t="s">
         <v>3515</v>
       </c>
@@ -40210,7 +40254,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="704" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A704" s="1" t="s">
         <v>3520</v>
       </c>
@@ -40251,7 +40295,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="705" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A705" s="1" t="s">
         <v>3525</v>
       </c>
@@ -40292,7 +40336,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="706" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A706" s="1" t="s">
         <v>3530</v>
       </c>
@@ -40333,7 +40377,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="707" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A707" s="1" t="s">
         <v>3535</v>
       </c>
@@ -40374,7 +40418,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="708" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A708" s="1" t="s">
         <v>3540</v>
       </c>
@@ -40415,7 +40459,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="709" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A709" s="1" t="s">
         <v>3545</v>
       </c>
@@ -40456,7 +40500,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="710" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A710" s="1" t="s">
         <v>3550</v>
       </c>
@@ -40497,7 +40541,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="711" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A711" s="1" t="s">
         <v>3555</v>
       </c>
@@ -40538,7 +40582,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="712" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A712" s="1" t="s">
         <v>3560</v>
       </c>
@@ -40579,7 +40623,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="713" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A713" s="1" t="s">
         <v>3565</v>
       </c>
@@ -40620,7 +40664,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="714" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A714" s="1" t="s">
         <v>3570</v>
       </c>
@@ -40661,7 +40705,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="715" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A715" s="1" t="s">
         <v>3575</v>
       </c>
@@ -40702,7 +40746,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="716" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A716" s="1" t="s">
         <v>3580</v>
       </c>
@@ -40743,7 +40787,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="717" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A717" s="1" t="s">
         <v>3585</v>
       </c>
@@ -40784,7 +40828,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="718" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A718" s="1" t="s">
         <v>3590</v>
       </c>
@@ -40825,7 +40869,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="719" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A719" s="1" t="s">
         <v>3595</v>
       </c>
@@ -40866,7 +40910,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="720" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A720" s="1" t="s">
         <v>3600</v>
       </c>
@@ -40907,7 +40951,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="721" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A721" s="1" t="s">
         <v>3605</v>
       </c>
@@ -40948,7 +40992,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="722" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A722" s="1" t="s">
         <v>3610</v>
       </c>
@@ -40989,7 +41033,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="723" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A723" s="1" t="s">
         <v>3615</v>
       </c>
@@ -41030,7 +41074,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="724" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A724" s="1" t="s">
         <v>3620</v>
       </c>
@@ -41071,7 +41115,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="725" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A725" s="1" t="s">
         <v>3625</v>
       </c>
@@ -41112,7 +41156,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="726" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A726" s="1" t="s">
         <v>3630</v>
       </c>
@@ -41153,7 +41197,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="727" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A727" s="1">
         <v>2000000001</v>
       </c>
@@ -41188,7 +41232,7 @@
       <c r="L727" s="1"/>
       <c r="M727" s="1"/>
     </row>
-    <row r="728" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A728" s="1">
         <v>2000000002</v>
       </c>
@@ -41223,7 +41267,7 @@
       <c r="L728" s="1"/>
       <c r="M728" s="1"/>
     </row>
-    <row r="729" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A729" s="1">
         <v>2000000003</v>
       </c>
@@ -41257,6 +41301,181 @@
       <c r="K729" s="1"/>
       <c r="L729" s="1"/>
       <c r="M729" s="1"/>
+    </row>
+    <row r="730" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A730" s="1">
+        <v>2000000004</v>
+      </c>
+      <c r="B730" s="1" t="s">
+        <v>3642</v>
+      </c>
+      <c r="C730" s="1" t="s">
+        <v>3641</v>
+      </c>
+      <c r="D730" s="2" t="s">
+        <v>3643</v>
+      </c>
+      <c r="E730" s="2">
+        <v>121.455274378542</v>
+      </c>
+      <c r="F730" s="2">
+        <v>25.040546827165201</v>
+      </c>
+      <c r="G730" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H730" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I730" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J730" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K730" s="1"/>
+      <c r="L730" s="1"/>
+      <c r="M730" s="1"/>
+    </row>
+    <row r="731" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A731" s="1">
+        <v>200000005</v>
+      </c>
+      <c r="B731" s="1" t="s">
+        <v>3642</v>
+      </c>
+      <c r="C731" s="1" t="s">
+        <v>3645</v>
+      </c>
+      <c r="D731" s="2" t="s">
+        <v>3644</v>
+      </c>
+      <c r="E731" s="2">
+        <v>121.48376668410199</v>
+      </c>
+      <c r="F731" s="2">
+        <v>25.062405319941899</v>
+      </c>
+      <c r="G731" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H731" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I731" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J731" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K731" s="1"/>
+      <c r="L731" s="1"/>
+      <c r="M731" s="1"/>
+    </row>
+    <row r="732" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A732" s="1">
+        <v>200000006</v>
+      </c>
+      <c r="B732" s="1" t="s">
+        <v>3642</v>
+      </c>
+      <c r="C732" s="1" t="s">
+        <v>3647</v>
+      </c>
+      <c r="D732" s="2" t="s">
+        <v>3646</v>
+      </c>
+      <c r="E732" s="2">
+        <v>121.36767133806801</v>
+      </c>
+      <c r="F732" s="2">
+        <v>25.059764493631999</v>
+      </c>
+      <c r="G732" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H732" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I732" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J732" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K732" s="1"/>
+      <c r="L732" s="1"/>
+      <c r="M732" s="1"/>
+    </row>
+    <row r="733" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A733" s="1">
+        <v>200000007</v>
+      </c>
+      <c r="B733" s="1" t="s">
+        <v>3642</v>
+      </c>
+      <c r="C733" s="1" t="s">
+        <v>3649</v>
+      </c>
+      <c r="D733" s="2" t="s">
+        <v>3648</v>
+      </c>
+      <c r="E733" s="2">
+        <v>121.464995251562</v>
+      </c>
+      <c r="F733" s="2">
+        <v>25.1391196305613</v>
+      </c>
+      <c r="G733" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H733" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I733" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J733" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K733" s="1"/>
+      <c r="L733" s="1"/>
+      <c r="M733" s="1"/>
+    </row>
+    <row r="734" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A734" s="1">
+        <v>200000008</v>
+      </c>
+      <c r="B734" s="1" t="s">
+        <v>3642</v>
+      </c>
+      <c r="C734" s="1" t="s">
+        <v>3651</v>
+      </c>
+      <c r="D734" s="2" t="s">
+        <v>3650</v>
+      </c>
+      <c r="E734" s="2">
+        <v>121.472280851561</v>
+      </c>
+      <c r="F734" s="2">
+        <v>25.123984726164899</v>
+      </c>
+      <c r="G734" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H734" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I734" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J734" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K734" s="1"/>
+      <c r="L734" s="1"/>
+      <c r="M734" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
@@ -41267,7 +41486,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.149999999999999" x14ac:dyDescent="0.45"/>
   <sheetData/>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -41277,7 +41496,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.149999999999999" x14ac:dyDescent="0.45"/>
   <sheetData/>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/store_info.xlsx
+++ b/data/store_info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeff0\OneDrive\桌面\115_NTUT_Thesis\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{743D5722-6E06-4CA8-A135-C52C58AA1AB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5FD0291-6576-4F00-BCED-4B35622CA9EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2820" yWindow="2025" windowWidth="32400" windowHeight="18855" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9494" uniqueCount="3652">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9522" uniqueCount="3660">
   <si>
     <t>店鋪編號</t>
   </si>
@@ -10993,6 +10993,38 @@
   </si>
   <si>
     <t>關渡慈濟店</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>新莊忠承店</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>新北市新莊區中平路377巷6號</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>三重新五華店</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>新北市三重區五華街83號1樓</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>林口正新店</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>華儷店</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>臺北市北投區西安街二段203號</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>新北市林口區中正路51號</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -11419,19 +11451,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M734"/>
-  <sheetFormatPr defaultRowHeight="16.149999999999999" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:M738"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.86328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.1328125" customWidth="1"/>
-    <col min="3" max="3" width="13.86328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="69.3984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="18.3984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="9.46484375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.125" customWidth="1"/>
+    <col min="3" max="3" width="13.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="69.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="18.375" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="9.5" bestFit="1" customWidth="1"/>
     <col min="11" max="13" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -11472,7 +11504,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
@@ -11513,7 +11545,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>23</v>
       </c>
@@ -11554,7 +11586,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>28</v>
       </c>
@@ -11595,7 +11627,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>33</v>
       </c>
@@ -11636,7 +11668,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>38</v>
       </c>
@@ -11677,7 +11709,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>43</v>
       </c>
@@ -11718,7 +11750,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>48</v>
       </c>
@@ -11759,7 +11791,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>53</v>
       </c>
@@ -11800,7 +11832,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>58</v>
       </c>
@@ -11841,7 +11873,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>63</v>
       </c>
@@ -11882,7 +11914,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>68</v>
       </c>
@@ -11923,7 +11955,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>73</v>
       </c>
@@ -11964,7 +11996,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>78</v>
       </c>
@@ -12005,7 +12037,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>83</v>
       </c>
@@ -12046,7 +12078,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>88</v>
       </c>
@@ -12087,7 +12119,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>93</v>
       </c>
@@ -12128,7 +12160,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>98</v>
       </c>
@@ -12169,7 +12201,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>103</v>
       </c>
@@ -12210,7 +12242,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>108</v>
       </c>
@@ -12251,7 +12283,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>113</v>
       </c>
@@ -12292,7 +12324,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>118</v>
       </c>
@@ -12333,7 +12365,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>123</v>
       </c>
@@ -12374,7 +12406,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>128</v>
       </c>
@@ -12415,7 +12447,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>133</v>
       </c>
@@ -12456,7 +12488,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>138</v>
       </c>
@@ -12497,7 +12529,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>143</v>
       </c>
@@ -12538,7 +12570,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>148</v>
       </c>
@@ -12579,7 +12611,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>153</v>
       </c>
@@ -12620,7 +12652,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>158</v>
       </c>
@@ -12661,7 +12693,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>163</v>
       </c>
@@ -12702,7 +12734,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>168</v>
       </c>
@@ -12743,7 +12775,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>173</v>
       </c>
@@ -12784,7 +12816,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>178</v>
       </c>
@@ -12825,7 +12857,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>183</v>
       </c>
@@ -12866,7 +12898,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>188</v>
       </c>
@@ -12907,7 +12939,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>193</v>
       </c>
@@ -12948,7 +12980,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>198</v>
       </c>
@@ -12989,7 +13021,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>203</v>
       </c>
@@ -13030,7 +13062,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>208</v>
       </c>
@@ -13071,7 +13103,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>213</v>
       </c>
@@ -13112,7 +13144,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>218</v>
       </c>
@@ -13153,7 +13185,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>223</v>
       </c>
@@ -13194,7 +13226,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>228</v>
       </c>
@@ -13235,7 +13267,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>233</v>
       </c>
@@ -13276,7 +13308,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>238</v>
       </c>
@@ -13317,7 +13349,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>243</v>
       </c>
@@ -13358,7 +13390,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>248</v>
       </c>
@@ -13399,7 +13431,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>253</v>
       </c>
@@ -13440,7 +13472,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>258</v>
       </c>
@@ -13481,7 +13513,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>263</v>
       </c>
@@ -13522,7 +13554,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>268</v>
       </c>
@@ -13563,7 +13595,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>273</v>
       </c>
@@ -13604,7 +13636,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>278</v>
       </c>
@@ -13645,7 +13677,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>283</v>
       </c>
@@ -13686,7 +13718,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>288</v>
       </c>
@@ -13727,7 +13759,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>293</v>
       </c>
@@ -13768,7 +13800,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>298</v>
       </c>
@@ -13809,7 +13841,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>303</v>
       </c>
@@ -13850,7 +13882,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>308</v>
       </c>
@@ -13891,7 +13923,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>313</v>
       </c>
@@ -13932,7 +13964,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>318</v>
       </c>
@@ -13973,7 +14005,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>323</v>
       </c>
@@ -14014,7 +14046,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>328</v>
       </c>
@@ -14055,7 +14087,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>333</v>
       </c>
@@ -14096,7 +14128,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>338</v>
       </c>
@@ -14137,7 +14169,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>343</v>
       </c>
@@ -14178,7 +14210,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>348</v>
       </c>
@@ -14219,7 +14251,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>353</v>
       </c>
@@ -14260,7 +14292,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>358</v>
       </c>
@@ -14301,7 +14333,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>363</v>
       </c>
@@ -14342,7 +14374,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>368</v>
       </c>
@@ -14383,7 +14415,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>373</v>
       </c>
@@ -14424,7 +14456,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>378</v>
       </c>
@@ -14465,7 +14497,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>383</v>
       </c>
@@ -14506,7 +14538,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>388</v>
       </c>
@@ -14547,7 +14579,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>393</v>
       </c>
@@ -14588,7 +14620,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>398</v>
       </c>
@@ -14629,7 +14661,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>403</v>
       </c>
@@ -14670,7 +14702,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>408</v>
       </c>
@@ -14711,7 +14743,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>413</v>
       </c>
@@ -14752,7 +14784,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>418</v>
       </c>
@@ -14793,7 +14825,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>423</v>
       </c>
@@ -14834,7 +14866,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>428</v>
       </c>
@@ -14875,7 +14907,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>433</v>
       </c>
@@ -14916,7 +14948,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>438</v>
       </c>
@@ -14957,7 +14989,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>443</v>
       </c>
@@ -14998,7 +15030,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>448</v>
       </c>
@@ -15039,7 +15071,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>453</v>
       </c>
@@ -15080,7 +15112,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>458</v>
       </c>
@@ -15121,7 +15153,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>463</v>
       </c>
@@ -15162,7 +15194,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>468</v>
       </c>
@@ -15203,7 +15235,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>473</v>
       </c>
@@ -15244,7 +15276,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>478</v>
       </c>
@@ -15285,7 +15317,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>483</v>
       </c>
@@ -15326,7 +15358,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>488</v>
       </c>
@@ -15367,7 +15399,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>493</v>
       </c>
@@ -15408,7 +15440,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>498</v>
       </c>
@@ -15449,7 +15481,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>503</v>
       </c>
@@ -15490,7 +15522,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>508</v>
       </c>
@@ -15531,7 +15563,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>513</v>
       </c>
@@ -15572,7 +15604,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>518</v>
       </c>
@@ -15613,7 +15645,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>523</v>
       </c>
@@ -15654,7 +15686,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>528</v>
       </c>
@@ -15695,7 +15727,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>533</v>
       </c>
@@ -15736,7 +15768,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>538</v>
       </c>
@@ -15777,7 +15809,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>543</v>
       </c>
@@ -15818,7 +15850,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>548</v>
       </c>
@@ -15859,7 +15891,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>553</v>
       </c>
@@ -15900,7 +15932,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>558</v>
       </c>
@@ -15941,7 +15973,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>563</v>
       </c>
@@ -15982,7 +16014,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>568</v>
       </c>
@@ -16023,7 +16055,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>573</v>
       </c>
@@ -16064,7 +16096,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>578</v>
       </c>
@@ -16105,7 +16137,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>583</v>
       </c>
@@ -16146,7 +16178,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>588</v>
       </c>
@@ -16187,7 +16219,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>593</v>
       </c>
@@ -16228,7 +16260,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>598</v>
       </c>
@@ -16269,7 +16301,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>603</v>
       </c>
@@ -16310,7 +16342,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>608</v>
       </c>
@@ -16351,7 +16383,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>613</v>
       </c>
@@ -16392,7 +16424,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>618</v>
       </c>
@@ -16433,7 +16465,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>623</v>
       </c>
@@ -16474,7 +16506,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>628</v>
       </c>
@@ -16515,7 +16547,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>633</v>
       </c>
@@ -16556,7 +16588,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>638</v>
       </c>
@@ -16597,7 +16629,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>643</v>
       </c>
@@ -16638,7 +16670,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>648</v>
       </c>
@@ -16679,7 +16711,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>653</v>
       </c>
@@ -16720,7 +16752,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>658</v>
       </c>
@@ -16761,7 +16793,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>663</v>
       </c>
@@ -16802,7 +16834,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>668</v>
       </c>
@@ -16843,7 +16875,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>673</v>
       </c>
@@ -16884,7 +16916,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>678</v>
       </c>
@@ -16925,7 +16957,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>683</v>
       </c>
@@ -16966,7 +16998,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>688</v>
       </c>
@@ -17007,7 +17039,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>693</v>
       </c>
@@ -17048,7 +17080,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>698</v>
       </c>
@@ -17089,7 +17121,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>703</v>
       </c>
@@ -17130,7 +17162,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>708</v>
       </c>
@@ -17171,7 +17203,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>713</v>
       </c>
@@ -17212,7 +17244,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>718</v>
       </c>
@@ -17253,7 +17285,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>723</v>
       </c>
@@ -17294,7 +17326,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>728</v>
       </c>
@@ -17335,7 +17367,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>733</v>
       </c>
@@ -17376,7 +17408,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>738</v>
       </c>
@@ -17417,7 +17449,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>743</v>
       </c>
@@ -17458,7 +17490,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>748</v>
       </c>
@@ -17499,7 +17531,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>753</v>
       </c>
@@ -17540,7 +17572,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>758</v>
       </c>
@@ -17581,7 +17613,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>763</v>
       </c>
@@ -17622,7 +17654,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
         <v>768</v>
       </c>
@@ -17663,7 +17695,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>773</v>
       </c>
@@ -17704,7 +17736,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>778</v>
       </c>
@@ -17745,7 +17777,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
         <v>783</v>
       </c>
@@ -17786,7 +17818,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
         <v>788</v>
       </c>
@@ -17827,7 +17859,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
         <v>793</v>
       </c>
@@ -17868,7 +17900,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
         <v>798</v>
       </c>
@@ -17909,7 +17941,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
         <v>803</v>
       </c>
@@ -17950,7 +17982,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
         <v>808</v>
       </c>
@@ -17991,7 +18023,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="161" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
         <v>813</v>
       </c>
@@ -18032,7 +18064,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="162" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
         <v>818</v>
       </c>
@@ -18073,7 +18105,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="163" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
         <v>823</v>
       </c>
@@ -18114,7 +18146,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="164" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
         <v>828</v>
       </c>
@@ -18155,7 +18187,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="165" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
         <v>833</v>
       </c>
@@ -18196,7 +18228,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="166" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
         <v>838</v>
       </c>
@@ -18237,7 +18269,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="167" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
         <v>843</v>
       </c>
@@ -18278,7 +18310,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="168" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
         <v>848</v>
       </c>
@@ -18319,7 +18351,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="169" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
         <v>853</v>
       </c>
@@ -18360,7 +18392,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="170" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
         <v>858</v>
       </c>
@@ -18401,7 +18433,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="171" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
         <v>863</v>
       </c>
@@ -18442,7 +18474,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="172" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
         <v>868</v>
       </c>
@@ -18483,7 +18515,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="173" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
         <v>873</v>
       </c>
@@ -18524,7 +18556,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="174" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
         <v>878</v>
       </c>
@@ -18565,7 +18597,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="175" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
         <v>883</v>
       </c>
@@ -18606,7 +18638,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="176" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
         <v>888</v>
       </c>
@@ -18647,7 +18679,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
         <v>893</v>
       </c>
@@ -18688,7 +18720,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="178" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
         <v>898</v>
       </c>
@@ -18729,7 +18761,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="179" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
         <v>903</v>
       </c>
@@ -18770,7 +18802,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
         <v>908</v>
       </c>
@@ -18811,7 +18843,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="181" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
         <v>913</v>
       </c>
@@ -18852,7 +18884,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="182" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
         <v>918</v>
       </c>
@@ -18893,7 +18925,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="183" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
         <v>923</v>
       </c>
@@ -18934,7 +18966,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="184" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
         <v>928</v>
       </c>
@@ -18975,7 +19007,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="185" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
         <v>933</v>
       </c>
@@ -19016,7 +19048,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="186" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="186" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
         <v>938</v>
       </c>
@@ -19057,7 +19089,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="187" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
         <v>943</v>
       </c>
@@ -19098,7 +19130,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="188" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="188" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
         <v>948</v>
       </c>
@@ -19139,7 +19171,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="189" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
         <v>953</v>
       </c>
@@ -19180,7 +19212,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="190" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
         <v>958</v>
       </c>
@@ -19221,7 +19253,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="191" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
         <v>963</v>
       </c>
@@ -19262,7 +19294,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="192" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="192" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
         <v>968</v>
       </c>
@@ -19303,7 +19335,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="193" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="193" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
         <v>973</v>
       </c>
@@ -19344,7 +19376,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="194" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="194" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
         <v>978</v>
       </c>
@@ -19385,7 +19417,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="195" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="195" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
         <v>983</v>
       </c>
@@ -19426,7 +19458,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="196" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="196" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
         <v>988</v>
       </c>
@@ -19467,7 +19499,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="197" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
         <v>993</v>
       </c>
@@ -19508,7 +19540,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="198" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="198" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
         <v>998</v>
       </c>
@@ -19549,7 +19581,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="199" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
         <v>1003</v>
       </c>
@@ -19590,7 +19622,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="200" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="200" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
         <v>1008</v>
       </c>
@@ -19631,7 +19663,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="201" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="201" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
         <v>1013</v>
       </c>
@@ -19672,7 +19704,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="202" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="202" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
         <v>1018</v>
       </c>
@@ -19713,7 +19745,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="203" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="203" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
         <v>1023</v>
       </c>
@@ -19754,7 +19786,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="204" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="204" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
         <v>1028</v>
       </c>
@@ -19795,7 +19827,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="205" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="205" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
         <v>1033</v>
       </c>
@@ -19836,7 +19868,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="206" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="206" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
         <v>1038</v>
       </c>
@@ -19877,7 +19909,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="207" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="207" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
         <v>1043</v>
       </c>
@@ -19918,7 +19950,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="208" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="208" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
         <v>1048</v>
       </c>
@@ -19959,7 +19991,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="209" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="209" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
         <v>1053</v>
       </c>
@@ -20000,7 +20032,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="210" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="210" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
         <v>1058</v>
       </c>
@@ -20041,7 +20073,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="211" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="211" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
         <v>1063</v>
       </c>
@@ -20082,7 +20114,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="212" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="212" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
         <v>1068</v>
       </c>
@@ -20123,7 +20155,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="213" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="213" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
         <v>1073</v>
       </c>
@@ -20164,7 +20196,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="214" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="214" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
         <v>1078</v>
       </c>
@@ -20205,7 +20237,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="215" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="215" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
         <v>1083</v>
       </c>
@@ -20246,7 +20278,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="216" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="216" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
         <v>1088</v>
       </c>
@@ -20287,7 +20319,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="217" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="217" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
         <v>1093</v>
       </c>
@@ -20328,7 +20360,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="218" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="218" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
         <v>1098</v>
       </c>
@@ -20369,7 +20401,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="219" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="219" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
         <v>1103</v>
       </c>
@@ -20410,7 +20442,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="220" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="220" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
         <v>1108</v>
       </c>
@@ -20451,7 +20483,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="221" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="221" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
         <v>1113</v>
       </c>
@@ -20492,7 +20524,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="222" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="222" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
         <v>1118</v>
       </c>
@@ -20533,7 +20565,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="223" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="223" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
         <v>1123</v>
       </c>
@@ -20574,7 +20606,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="224" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="224" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
         <v>1128</v>
       </c>
@@ -20615,7 +20647,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="225" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="225" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
         <v>1133</v>
       </c>
@@ -20656,7 +20688,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="226" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="226" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
         <v>1138</v>
       </c>
@@ -20697,7 +20729,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="227" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="227" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
         <v>1143</v>
       </c>
@@ -20738,7 +20770,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="228" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="228" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
         <v>1148</v>
       </c>
@@ -20779,7 +20811,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="229" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="229" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
         <v>1153</v>
       </c>
@@ -20820,7 +20852,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="230" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="230" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
         <v>1158</v>
       </c>
@@ -20861,7 +20893,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="231" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="231" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
         <v>1163</v>
       </c>
@@ -20902,7 +20934,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="232" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="232" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
         <v>1168</v>
       </c>
@@ -20943,7 +20975,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="233" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="233" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
         <v>1173</v>
       </c>
@@ -20984,7 +21016,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="234" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="234" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
         <v>1178</v>
       </c>
@@ -21025,7 +21057,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="235" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="235" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
         <v>1183</v>
       </c>
@@ -21066,7 +21098,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="236" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="236" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
         <v>1188</v>
       </c>
@@ -21107,7 +21139,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="237" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="237" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
         <v>1193</v>
       </c>
@@ -21148,7 +21180,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="238" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="238" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
         <v>1198</v>
       </c>
@@ -21189,7 +21221,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="239" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="239" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
         <v>1203</v>
       </c>
@@ -21230,7 +21262,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="240" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="240" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
         <v>1208</v>
       </c>
@@ -21271,7 +21303,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="241" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="241" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
         <v>1213</v>
       </c>
@@ -21312,7 +21344,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="242" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="242" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
         <v>1218</v>
       </c>
@@ -21353,7 +21385,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="243" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="243" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
         <v>1223</v>
       </c>
@@ -21394,7 +21426,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="244" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="244" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
         <v>1228</v>
       </c>
@@ -21435,7 +21467,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="245" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="245" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
         <v>1233</v>
       </c>
@@ -21476,7 +21508,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="246" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="246" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
         <v>1238</v>
       </c>
@@ -21517,7 +21549,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="247" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="247" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
         <v>1243</v>
       </c>
@@ -21558,7 +21590,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="248" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="248" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
         <v>1248</v>
       </c>
@@ -21599,7 +21631,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="249" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="249" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
         <v>1253</v>
       </c>
@@ -21640,7 +21672,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="250" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="250" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
         <v>1258</v>
       </c>
@@ -21681,7 +21713,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="251" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="251" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
         <v>1263</v>
       </c>
@@ -21722,7 +21754,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="252" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="252" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
         <v>1268</v>
       </c>
@@ -21763,7 +21795,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="253" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="253" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
         <v>1273</v>
       </c>
@@ -21804,7 +21836,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="254" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="254" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
         <v>1278</v>
       </c>
@@ -21845,7 +21877,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="255" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="255" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
         <v>1283</v>
       </c>
@@ -21886,7 +21918,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="256" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="256" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
         <v>1288</v>
       </c>
@@ -21927,7 +21959,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="257" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="257" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
         <v>1293</v>
       </c>
@@ -21968,7 +22000,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="258" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="258" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
         <v>1298</v>
       </c>
@@ -22009,7 +22041,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="259" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="259" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
         <v>1303</v>
       </c>
@@ -22050,7 +22082,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="260" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="260" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
         <v>1308</v>
       </c>
@@ -22091,7 +22123,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="261" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="261" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
         <v>1313</v>
       </c>
@@ -22132,7 +22164,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="262" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="262" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
         <v>1318</v>
       </c>
@@ -22173,7 +22205,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="263" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="263" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
         <v>1323</v>
       </c>
@@ -22214,7 +22246,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="264" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="264" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
         <v>1328</v>
       </c>
@@ -22255,7 +22287,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="265" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="265" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
         <v>1333</v>
       </c>
@@ -22296,7 +22328,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="266" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="266" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
         <v>1338</v>
       </c>
@@ -22337,7 +22369,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="267" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="267" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
         <v>1343</v>
       </c>
@@ -22378,7 +22410,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="268" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="268" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
         <v>1348</v>
       </c>
@@ -22419,7 +22451,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="269" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="269" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
         <v>1353</v>
       </c>
@@ -22460,7 +22492,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="270" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="270" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
         <v>1358</v>
       </c>
@@ -22501,7 +22533,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="271" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="271" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
         <v>1363</v>
       </c>
@@ -22542,7 +22574,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="272" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="272" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
         <v>1368</v>
       </c>
@@ -22583,7 +22615,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="273" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="273" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
         <v>1373</v>
       </c>
@@ -22624,7 +22656,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="274" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="274" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
         <v>1378</v>
       </c>
@@ -22665,7 +22697,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="275" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="275" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
         <v>1383</v>
       </c>
@@ -22706,7 +22738,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="276" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="276" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
         <v>1388</v>
       </c>
@@ -22747,7 +22779,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="277" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="277" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
         <v>1393</v>
       </c>
@@ -22788,7 +22820,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="278" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="278" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
         <v>1398</v>
       </c>
@@ -22829,7 +22861,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="279" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="279" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
         <v>1403</v>
       </c>
@@ -22870,7 +22902,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="280" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="280" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
         <v>1408</v>
       </c>
@@ -22911,7 +22943,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="281" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="281" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
         <v>1413</v>
       </c>
@@ -22952,7 +22984,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="282" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="282" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
         <v>1418</v>
       </c>
@@ -22993,7 +23025,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="283" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="283" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
         <v>1423</v>
       </c>
@@ -23034,7 +23066,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="284" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="284" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
         <v>1428</v>
       </c>
@@ -23075,7 +23107,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="285" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="285" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
         <v>1433</v>
       </c>
@@ -23116,7 +23148,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="286" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="286" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
         <v>1438</v>
       </c>
@@ -23157,7 +23189,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="287" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="287" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
         <v>1443</v>
       </c>
@@ -23198,7 +23230,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="288" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="288" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
         <v>1448</v>
       </c>
@@ -23239,7 +23271,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="289" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="289" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
         <v>1453</v>
       </c>
@@ -23280,7 +23312,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="290" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="290" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
         <v>1458</v>
       </c>
@@ -23321,7 +23353,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="291" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="291" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
         <v>1463</v>
       </c>
@@ -23362,7 +23394,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="292" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="292" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
         <v>1468</v>
       </c>
@@ -23403,7 +23435,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="293" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="293" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
         <v>1473</v>
       </c>
@@ -23444,7 +23476,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="294" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="294" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
         <v>1478</v>
       </c>
@@ -23485,7 +23517,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="295" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="295" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
         <v>1483</v>
       </c>
@@ -23526,7 +23558,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="296" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="296" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
         <v>1488</v>
       </c>
@@ -23567,7 +23599,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="297" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="297" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
         <v>1493</v>
       </c>
@@ -23608,7 +23640,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="298" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="298" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
         <v>1498</v>
       </c>
@@ -23649,7 +23681,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="299" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="299" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
         <v>1503</v>
       </c>
@@ -23690,7 +23722,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="300" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="300" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
         <v>1508</v>
       </c>
@@ -23731,7 +23763,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="301" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="301" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
         <v>1513</v>
       </c>
@@ -23772,7 +23804,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="302" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="302" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
         <v>1518</v>
       </c>
@@ -23813,7 +23845,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="303" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="303" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
         <v>1523</v>
       </c>
@@ -23854,7 +23886,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="304" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="304" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A304" s="1" t="s">
         <v>1528</v>
       </c>
@@ -23895,7 +23927,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="305" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="305" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A305" s="1" t="s">
         <v>1533</v>
       </c>
@@ -23936,7 +23968,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="306" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="306" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A306" s="1" t="s">
         <v>1538</v>
       </c>
@@ -23977,7 +24009,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="307" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="307" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="s">
         <v>1543</v>
       </c>
@@ -24018,7 +24050,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="308" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="308" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A308" s="1" t="s">
         <v>1548</v>
       </c>
@@ -24059,7 +24091,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="309" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="309" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A309" s="1" t="s">
         <v>1553</v>
       </c>
@@ -24100,7 +24132,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="310" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="310" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A310" s="1" t="s">
         <v>1558</v>
       </c>
@@ -24141,7 +24173,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="311" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="311" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
         <v>1563</v>
       </c>
@@ -24182,7 +24214,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="312" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="312" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
         <v>1568</v>
       </c>
@@ -24223,7 +24255,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="313" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="313" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="s">
         <v>1573</v>
       </c>
@@ -24264,7 +24296,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="314" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="314" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A314" s="1" t="s">
         <v>1578</v>
       </c>
@@ -24305,7 +24337,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="315" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="315" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A315" s="1" t="s">
         <v>1583</v>
       </c>
@@ -24346,7 +24378,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="316" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="316" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
         <v>1588</v>
       </c>
@@ -24387,7 +24419,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="317" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="317" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
         <v>1593</v>
       </c>
@@ -24428,7 +24460,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="318" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="318" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="s">
         <v>1598</v>
       </c>
@@ -24469,7 +24501,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="319" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="319" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="s">
         <v>1603</v>
       </c>
@@ -24510,7 +24542,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="320" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="320" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
         <v>1608</v>
       </c>
@@ -24551,7 +24583,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="321" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="321" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
         <v>1613</v>
       </c>
@@ -24592,7 +24624,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="322" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="322" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="s">
         <v>1618</v>
       </c>
@@ -24633,7 +24665,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="323" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="323" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A323" s="1" t="s">
         <v>1623</v>
       </c>
@@ -24674,7 +24706,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="324" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="324" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A324" s="1" t="s">
         <v>1628</v>
       </c>
@@ -24715,7 +24747,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="325" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="325" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A325" s="1" t="s">
         <v>1633</v>
       </c>
@@ -24756,7 +24788,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="326" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="326" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A326" s="1" t="s">
         <v>1638</v>
       </c>
@@ -24797,7 +24829,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="327" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="327" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
         <v>1643</v>
       </c>
@@ -24838,7 +24870,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="328" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="328" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
         <v>1648</v>
       </c>
@@ -24879,7 +24911,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="329" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="329" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
         <v>1653</v>
       </c>
@@ -24920,7 +24952,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="330" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="330" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="s">
         <v>1658</v>
       </c>
@@ -24961,7 +24993,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="331" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="331" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="s">
         <v>1663</v>
       </c>
@@ -25002,7 +25034,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="332" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="332" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
         <v>1668</v>
       </c>
@@ -25043,7 +25075,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="333" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="333" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
         <v>1673</v>
       </c>
@@ -25084,7 +25116,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="334" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="334" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A334" s="1" t="s">
         <v>1678</v>
       </c>
@@ -25125,7 +25157,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="335" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="335" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A335" s="1" t="s">
         <v>1683</v>
       </c>
@@ -25166,7 +25198,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="336" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="336" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A336" s="1" t="s">
         <v>1688</v>
       </c>
@@ -25207,7 +25239,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="337" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="337" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="s">
         <v>1693</v>
       </c>
@@ -25248,7 +25280,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="338" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="338" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
         <v>1698</v>
       </c>
@@ -25289,7 +25321,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="339" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="339" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="s">
         <v>1703</v>
       </c>
@@ -25330,7 +25362,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="340" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="340" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A340" s="1" t="s">
         <v>1708</v>
       </c>
@@ -25371,7 +25403,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="341" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="341" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A341" s="1" t="s">
         <v>1713</v>
       </c>
@@ -25412,7 +25444,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="342" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="342" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A342" s="1" t="s">
         <v>1718</v>
       </c>
@@ -25453,7 +25485,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="343" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="343" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A343" s="1" t="s">
         <v>1723</v>
       </c>
@@ -25494,7 +25526,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="344" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="344" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A344" s="1" t="s">
         <v>1728</v>
       </c>
@@ -25535,7 +25567,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="345" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="345" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="s">
         <v>1733</v>
       </c>
@@ -25576,7 +25608,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="346" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="346" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="s">
         <v>1738</v>
       </c>
@@ -25617,7 +25649,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="347" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="347" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
         <v>1743</v>
       </c>
@@ -25658,7 +25690,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="348" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="348" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A348" s="1" t="s">
         <v>1748</v>
       </c>
@@ -25699,7 +25731,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="349" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="349" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A349" s="1" t="s">
         <v>1753</v>
       </c>
@@ -25740,7 +25772,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="350" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="350" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="s">
         <v>1758</v>
       </c>
@@ -25781,7 +25813,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="351" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="351" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="s">
         <v>1763</v>
       </c>
@@ -25822,7 +25854,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="352" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="352" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="s">
         <v>1768</v>
       </c>
@@ -25863,7 +25895,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="353" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="353" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A353" s="1" t="s">
         <v>1773</v>
       </c>
@@ -25904,7 +25936,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="354" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="354" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A354" s="1" t="s">
         <v>1778</v>
       </c>
@@ -25945,7 +25977,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="355" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="355" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A355" s="1" t="s">
         <v>1783</v>
       </c>
@@ -25986,7 +26018,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="356" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="356" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A356" s="1" t="s">
         <v>1788</v>
       </c>
@@ -26027,7 +26059,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="357" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="357" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A357" s="1" t="s">
         <v>1793</v>
       </c>
@@ -26068,7 +26100,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="358" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="358" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A358" s="1" t="s">
         <v>1798</v>
       </c>
@@ -26109,7 +26141,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="359" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="359" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A359" s="1" t="s">
         <v>1803</v>
       </c>
@@ -26150,7 +26182,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="360" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="360" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A360" s="1" t="s">
         <v>1808</v>
       </c>
@@ -26191,7 +26223,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="361" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="361" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A361" s="1" t="s">
         <v>1813</v>
       </c>
@@ -26232,7 +26264,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="362" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="362" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A362" s="1" t="s">
         <v>1818</v>
       </c>
@@ -26273,7 +26305,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="363" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="363" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A363" s="1" t="s">
         <v>1823</v>
       </c>
@@ -26314,7 +26346,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="364" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="364" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A364" s="1" t="s">
         <v>1828</v>
       </c>
@@ -26355,7 +26387,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="365" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="365" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A365" s="1" t="s">
         <v>1833</v>
       </c>
@@ -26396,7 +26428,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="366" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="366" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A366" s="1" t="s">
         <v>1838</v>
       </c>
@@ -26437,7 +26469,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="367" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="367" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A367" s="1" t="s">
         <v>1843</v>
       </c>
@@ -26478,7 +26510,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="368" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="368" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A368" s="1" t="s">
         <v>1848</v>
       </c>
@@ -26519,7 +26551,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="369" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="369" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A369" s="1" t="s">
         <v>1853</v>
       </c>
@@ -26560,7 +26592,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="370" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="370" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A370" s="1" t="s">
         <v>1858</v>
       </c>
@@ -26601,7 +26633,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="371" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="371" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A371" s="1" t="s">
         <v>1863</v>
       </c>
@@ -26642,7 +26674,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="372" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="372" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A372" s="1" t="s">
         <v>1868</v>
       </c>
@@ -26683,7 +26715,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="373" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="373" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A373" s="1" t="s">
         <v>1873</v>
       </c>
@@ -26724,7 +26756,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="374" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="374" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A374" s="1" t="s">
         <v>1878</v>
       </c>
@@ -26765,7 +26797,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="375" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="375" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A375" s="1" t="s">
         <v>1883</v>
       </c>
@@ -26806,7 +26838,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="376" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="376" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A376" s="1" t="s">
         <v>1888</v>
       </c>
@@ -26847,7 +26879,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="377" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="377" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A377" s="1" t="s">
         <v>1893</v>
       </c>
@@ -26888,7 +26920,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="378" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="378" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A378" s="1" t="s">
         <v>1898</v>
       </c>
@@ -26929,7 +26961,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="379" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="379" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A379" s="1" t="s">
         <v>1903</v>
       </c>
@@ -26970,7 +27002,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="380" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="380" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A380" s="1" t="s">
         <v>1908</v>
       </c>
@@ -27011,7 +27043,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="381" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="381" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A381" s="1" t="s">
         <v>1913</v>
       </c>
@@ -27052,7 +27084,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="382" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="382" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A382" s="1" t="s">
         <v>1918</v>
       </c>
@@ -27093,7 +27125,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="383" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="383" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A383" s="1" t="s">
         <v>1923</v>
       </c>
@@ -27134,7 +27166,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="384" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="384" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A384" s="1" t="s">
         <v>1928</v>
       </c>
@@ -27175,7 +27207,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="385" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="385" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A385" s="1" t="s">
         <v>1933</v>
       </c>
@@ -27216,7 +27248,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="386" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="386" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A386" s="1" t="s">
         <v>1938</v>
       </c>
@@ -27257,7 +27289,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="387" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="387" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A387" s="1" t="s">
         <v>1943</v>
       </c>
@@ -27298,7 +27330,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="388" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="388" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A388" s="1" t="s">
         <v>1948</v>
       </c>
@@ -27339,7 +27371,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="389" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="389" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A389" s="1" t="s">
         <v>1953</v>
       </c>
@@ -27380,7 +27412,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="390" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="390" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A390" s="1" t="s">
         <v>1958</v>
       </c>
@@ -27421,7 +27453,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="391" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="391" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A391" s="1" t="s">
         <v>1963</v>
       </c>
@@ -27462,7 +27494,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="392" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="392" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A392" s="1" t="s">
         <v>1968</v>
       </c>
@@ -27503,7 +27535,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="393" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="393" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A393" s="1" t="s">
         <v>1973</v>
       </c>
@@ -27544,7 +27576,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="394" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="394" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A394" s="1" t="s">
         <v>1978</v>
       </c>
@@ -27585,7 +27617,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="395" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="395" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A395" s="1" t="s">
         <v>1983</v>
       </c>
@@ -27626,7 +27658,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="396" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="396" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A396" s="1" t="s">
         <v>1988</v>
       </c>
@@ -27667,7 +27699,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="397" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="397" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A397" s="1" t="s">
         <v>1993</v>
       </c>
@@ -27708,7 +27740,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="398" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="398" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A398" s="1" t="s">
         <v>1998</v>
       </c>
@@ -27749,7 +27781,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="399" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="399" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A399" s="1" t="s">
         <v>2003</v>
       </c>
@@ -27790,7 +27822,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="400" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="400" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A400" s="1" t="s">
         <v>2008</v>
       </c>
@@ -27831,7 +27863,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="401" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="401" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A401" s="1" t="s">
         <v>2013</v>
       </c>
@@ -27872,7 +27904,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="402" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="402" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A402" s="1" t="s">
         <v>2018</v>
       </c>
@@ -27913,7 +27945,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="403" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="403" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A403" s="1" t="s">
         <v>2023</v>
       </c>
@@ -27954,7 +27986,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="404" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="404" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A404" s="1" t="s">
         <v>2028</v>
       </c>
@@ -27995,7 +28027,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="405" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="405" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A405" s="1" t="s">
         <v>2033</v>
       </c>
@@ -28036,7 +28068,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="406" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="406" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A406" s="1" t="s">
         <v>2038</v>
       </c>
@@ -28077,7 +28109,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="407" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="407" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A407" s="1" t="s">
         <v>2043</v>
       </c>
@@ -28118,7 +28150,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="408" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="408" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A408" s="1" t="s">
         <v>2048</v>
       </c>
@@ -28159,7 +28191,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="409" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="409" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A409" s="1" t="s">
         <v>2053</v>
       </c>
@@ -28200,7 +28232,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="410" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="410" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A410" s="1" t="s">
         <v>2058</v>
       </c>
@@ -28241,7 +28273,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="411" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="411" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A411" s="1" t="s">
         <v>2063</v>
       </c>
@@ -28282,7 +28314,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="412" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="412" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A412" s="1" t="s">
         <v>2068</v>
       </c>
@@ -28323,7 +28355,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="413" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="413" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A413" s="1" t="s">
         <v>2073</v>
       </c>
@@ -28364,7 +28396,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="414" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="414" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A414" s="1" t="s">
         <v>2078</v>
       </c>
@@ -28405,7 +28437,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="415" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="415" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A415" s="1" t="s">
         <v>2083</v>
       </c>
@@ -28446,7 +28478,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="416" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="416" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A416" s="1" t="s">
         <v>2088</v>
       </c>
@@ -28487,7 +28519,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="417" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="417" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A417" s="1" t="s">
         <v>2093</v>
       </c>
@@ -28528,7 +28560,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="418" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="418" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A418" s="1" t="s">
         <v>2098</v>
       </c>
@@ -28569,7 +28601,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="419" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="419" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A419" s="1" t="s">
         <v>2103</v>
       </c>
@@ -28610,7 +28642,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="420" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="420" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A420" s="1" t="s">
         <v>2108</v>
       </c>
@@ -28651,7 +28683,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="421" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="421" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A421" s="1" t="s">
         <v>2113</v>
       </c>
@@ -28692,7 +28724,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="422" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="422" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A422" s="1" t="s">
         <v>2118</v>
       </c>
@@ -28733,7 +28765,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="423" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="423" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A423" s="1" t="s">
         <v>2123</v>
       </c>
@@ -28774,7 +28806,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="424" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="424" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A424" s="1" t="s">
         <v>2128</v>
       </c>
@@ -28815,7 +28847,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="425" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="425" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A425" s="1" t="s">
         <v>2133</v>
       </c>
@@ -28856,7 +28888,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="426" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="426" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A426" s="1" t="s">
         <v>2138</v>
       </c>
@@ -28897,7 +28929,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="427" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="427" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A427" s="1" t="s">
         <v>2143</v>
       </c>
@@ -28938,7 +28970,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="428" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="428" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A428" s="1" t="s">
         <v>2148</v>
       </c>
@@ -28979,7 +29011,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="429" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="429" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A429" s="1" t="s">
         <v>2153</v>
       </c>
@@ -29020,7 +29052,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="430" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="430" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A430" s="1" t="s">
         <v>2158</v>
       </c>
@@ -29061,7 +29093,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="431" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="431" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A431" s="1" t="s">
         <v>2163</v>
       </c>
@@ -29102,7 +29134,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="432" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="432" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A432" s="1" t="s">
         <v>2168</v>
       </c>
@@ -29143,7 +29175,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="433" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="433" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A433" s="1" t="s">
         <v>2173</v>
       </c>
@@ -29184,7 +29216,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="434" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="434" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A434" s="1" t="s">
         <v>2178</v>
       </c>
@@ -29225,7 +29257,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="435" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="435" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A435" s="1" t="s">
         <v>2183</v>
       </c>
@@ -29266,7 +29298,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="436" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="436" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A436" s="1" t="s">
         <v>2188</v>
       </c>
@@ -29307,7 +29339,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="437" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="437" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A437" s="1" t="s">
         <v>2193</v>
       </c>
@@ -29348,7 +29380,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="438" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="438" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A438" s="1" t="s">
         <v>2198</v>
       </c>
@@ -29389,7 +29421,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="439" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="439" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A439" s="1" t="s">
         <v>2203</v>
       </c>
@@ -29430,7 +29462,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="440" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="440" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A440" s="1" t="s">
         <v>2208</v>
       </c>
@@ -29471,7 +29503,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="441" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="441" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A441" s="1" t="s">
         <v>2213</v>
       </c>
@@ -29512,7 +29544,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="442" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="442" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A442" s="1" t="s">
         <v>2218</v>
       </c>
@@ -29553,7 +29585,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="443" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="443" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A443" s="1" t="s">
         <v>2223</v>
       </c>
@@ -29594,7 +29626,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="444" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="444" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A444" s="1" t="s">
         <v>2228</v>
       </c>
@@ -29635,7 +29667,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="445" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="445" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A445" s="1" t="s">
         <v>2233</v>
       </c>
@@ -29676,7 +29708,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="446" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="446" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A446" s="1" t="s">
         <v>2238</v>
       </c>
@@ -29717,7 +29749,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="447" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="447" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A447" s="1" t="s">
         <v>2243</v>
       </c>
@@ -29758,7 +29790,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="448" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="448" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A448" s="1" t="s">
         <v>2248</v>
       </c>
@@ -29799,7 +29831,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="449" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="449" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A449" s="1" t="s">
         <v>2253</v>
       </c>
@@ -29840,7 +29872,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="450" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="450" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A450" s="1" t="s">
         <v>2258</v>
       </c>
@@ -29881,7 +29913,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="451" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="451" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A451" s="1" t="s">
         <v>2263</v>
       </c>
@@ -29922,7 +29954,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="452" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="452" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A452" s="1" t="s">
         <v>2268</v>
       </c>
@@ -29963,7 +29995,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="453" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="453" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A453" s="1" t="s">
         <v>2273</v>
       </c>
@@ -30004,7 +30036,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="454" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="454" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A454" s="1" t="s">
         <v>2278</v>
       </c>
@@ -30045,7 +30077,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="455" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="455" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A455" s="1" t="s">
         <v>2281</v>
       </c>
@@ -30086,7 +30118,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="456" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="456" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A456" s="1" t="s">
         <v>2286</v>
       </c>
@@ -30127,7 +30159,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="457" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="457" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A457" s="1" t="s">
         <v>2291</v>
       </c>
@@ -30168,7 +30200,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="458" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="458" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A458" s="1" t="s">
         <v>2296</v>
       </c>
@@ -30209,7 +30241,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="459" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="459" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A459" s="1" t="s">
         <v>2301</v>
       </c>
@@ -30250,7 +30282,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="460" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="460" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A460" s="1" t="s">
         <v>2306</v>
       </c>
@@ -30291,7 +30323,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="461" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="461" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A461" s="1" t="s">
         <v>2311</v>
       </c>
@@ -30332,7 +30364,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="462" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="462" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A462" s="1" t="s">
         <v>2316</v>
       </c>
@@ -30373,7 +30405,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="463" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="463" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A463" s="1" t="s">
         <v>2321</v>
       </c>
@@ -30414,7 +30446,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="464" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="464" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A464" s="1" t="s">
         <v>2326</v>
       </c>
@@ -30455,7 +30487,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="465" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="465" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A465" s="1" t="s">
         <v>2331</v>
       </c>
@@ -30496,7 +30528,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="466" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="466" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A466" s="1" t="s">
         <v>2334</v>
       </c>
@@ -30537,7 +30569,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="467" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="467" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A467" s="1" t="s">
         <v>2337</v>
       </c>
@@ -30578,7 +30610,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="468" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="468" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A468" s="1" t="s">
         <v>2342</v>
       </c>
@@ -30619,7 +30651,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="469" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="469" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A469" s="1" t="s">
         <v>2347</v>
       </c>
@@ -30660,7 +30692,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="470" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="470" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A470" s="1" t="s">
         <v>2352</v>
       </c>
@@ -30701,7 +30733,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="471" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="471" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A471" s="1" t="s">
         <v>2357</v>
       </c>
@@ -30742,7 +30774,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="472" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="472" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A472" s="1" t="s">
         <v>2362</v>
       </c>
@@ -30783,7 +30815,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="473" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="473" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A473" s="1" t="s">
         <v>2367</v>
       </c>
@@ -30824,7 +30856,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="474" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="474" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A474" s="1" t="s">
         <v>2372</v>
       </c>
@@ -30865,7 +30897,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="475" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="475" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A475" s="1" t="s">
         <v>2377</v>
       </c>
@@ -30906,7 +30938,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="476" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="476" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A476" s="1" t="s">
         <v>2382</v>
       </c>
@@ -30947,7 +30979,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="477" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="477" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A477" s="1" t="s">
         <v>2387</v>
       </c>
@@ -30988,7 +31020,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="478" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="478" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A478" s="1" t="s">
         <v>2392</v>
       </c>
@@ -31029,7 +31061,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="479" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="479" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A479" s="1" t="s">
         <v>2397</v>
       </c>
@@ -31070,7 +31102,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="480" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="480" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A480" s="1" t="s">
         <v>2402</v>
       </c>
@@ -31111,7 +31143,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="481" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="481" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A481" s="1" t="s">
         <v>2407</v>
       </c>
@@ -31152,7 +31184,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="482" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="482" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A482" s="1" t="s">
         <v>2412</v>
       </c>
@@ -31193,7 +31225,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="483" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="483" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A483" s="1" t="s">
         <v>2417</v>
       </c>
@@ -31234,7 +31266,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="484" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="484" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A484" s="1" t="s">
         <v>2422</v>
       </c>
@@ -31275,7 +31307,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="485" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="485" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A485" s="1" t="s">
         <v>2427</v>
       </c>
@@ -31316,7 +31348,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="486" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="486" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A486" s="1" t="s">
         <v>2432</v>
       </c>
@@ -31357,7 +31389,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="487" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="487" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A487" s="1" t="s">
         <v>2437</v>
       </c>
@@ -31398,7 +31430,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="488" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="488" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A488" s="1" t="s">
         <v>2442</v>
       </c>
@@ -31439,7 +31471,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="489" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="489" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A489" s="1" t="s">
         <v>2447</v>
       </c>
@@ -31480,7 +31512,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="490" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="490" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A490" s="1" t="s">
         <v>2452</v>
       </c>
@@ -31521,7 +31553,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="491" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="491" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A491" s="1" t="s">
         <v>2457</v>
       </c>
@@ -31562,7 +31594,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="492" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="492" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A492" s="1" t="s">
         <v>2462</v>
       </c>
@@ -31603,7 +31635,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="493" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="493" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A493" s="1" t="s">
         <v>2467</v>
       </c>
@@ -31644,7 +31676,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="494" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="494" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A494" s="1" t="s">
         <v>2472</v>
       </c>
@@ -31685,7 +31717,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="495" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="495" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A495" s="1" t="s">
         <v>2477</v>
       </c>
@@ -31726,7 +31758,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="496" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="496" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A496" s="1" t="s">
         <v>2482</v>
       </c>
@@ -31767,7 +31799,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="497" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="497" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A497" s="1" t="s">
         <v>2487</v>
       </c>
@@ -31808,7 +31840,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="498" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="498" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A498" s="1" t="s">
         <v>2492</v>
       </c>
@@ -31849,7 +31881,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="499" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="499" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A499" s="1" t="s">
         <v>2497</v>
       </c>
@@ -31890,7 +31922,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="500" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="500" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A500" s="1" t="s">
         <v>2502</v>
       </c>
@@ -31931,7 +31963,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="501" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="501" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A501" s="1" t="s">
         <v>2507</v>
       </c>
@@ -31972,7 +32004,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="502" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="502" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A502" s="1" t="s">
         <v>2512</v>
       </c>
@@ -32013,7 +32045,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="503" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="503" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A503" s="1" t="s">
         <v>2517</v>
       </c>
@@ -32054,7 +32086,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="504" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="504" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A504" s="1" t="s">
         <v>2522</v>
       </c>
@@ -32095,7 +32127,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="505" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="505" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A505" s="1" t="s">
         <v>2527</v>
       </c>
@@ -32136,7 +32168,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="506" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="506" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A506" s="1" t="s">
         <v>2532</v>
       </c>
@@ -32177,7 +32209,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="507" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="507" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A507" s="1" t="s">
         <v>2537</v>
       </c>
@@ -32218,7 +32250,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="508" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="508" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A508" s="1" t="s">
         <v>2542</v>
       </c>
@@ -32259,7 +32291,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="509" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="509" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A509" s="1" t="s">
         <v>2547</v>
       </c>
@@ -32300,7 +32332,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="510" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="510" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A510" s="1" t="s">
         <v>2552</v>
       </c>
@@ -32341,7 +32373,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="511" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="511" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A511" s="1" t="s">
         <v>2557</v>
       </c>
@@ -32382,7 +32414,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="512" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="512" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A512" s="1" t="s">
         <v>2562</v>
       </c>
@@ -32423,7 +32455,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="513" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="513" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A513" s="1" t="s">
         <v>2567</v>
       </c>
@@ -32464,7 +32496,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="514" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="514" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A514" s="1" t="s">
         <v>2572</v>
       </c>
@@ -32505,7 +32537,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="515" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="515" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A515" s="1" t="s">
         <v>2577</v>
       </c>
@@ -32546,7 +32578,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="516" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="516" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A516" s="1" t="s">
         <v>2582</v>
       </c>
@@ -32587,7 +32619,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="517" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="517" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A517" s="1" t="s">
         <v>2587</v>
       </c>
@@ -32628,7 +32660,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="518" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="518" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A518" s="1" t="s">
         <v>2592</v>
       </c>
@@ -32669,7 +32701,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="519" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="519" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A519" s="1" t="s">
         <v>2597</v>
       </c>
@@ -32710,7 +32742,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="520" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="520" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A520" s="1" t="s">
         <v>2602</v>
       </c>
@@ -32751,7 +32783,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="521" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="521" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A521" s="1" t="s">
         <v>2607</v>
       </c>
@@ -32792,7 +32824,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="522" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="522" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A522" s="1" t="s">
         <v>2612</v>
       </c>
@@ -32833,7 +32865,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="523" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="523" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A523" s="1" t="s">
         <v>2617</v>
       </c>
@@ -32874,7 +32906,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="524" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="524" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A524" s="1" t="s">
         <v>2622</v>
       </c>
@@ -32915,7 +32947,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="525" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="525" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A525" s="1" t="s">
         <v>2627</v>
       </c>
@@ -32956,7 +32988,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="526" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="526" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A526" s="1" t="s">
         <v>2632</v>
       </c>
@@ -32997,7 +33029,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="527" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="527" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A527" s="1" t="s">
         <v>2637</v>
       </c>
@@ -33038,7 +33070,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="528" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="528" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A528" s="1" t="s">
         <v>2642</v>
       </c>
@@ -33079,7 +33111,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="529" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="529" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A529" s="1" t="s">
         <v>2647</v>
       </c>
@@ -33120,7 +33152,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="530" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="530" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A530" s="1" t="s">
         <v>2652</v>
       </c>
@@ -33161,7 +33193,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="531" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="531" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A531" s="1" t="s">
         <v>2657</v>
       </c>
@@ -33202,7 +33234,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="532" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="532" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A532" s="1" t="s">
         <v>2662</v>
       </c>
@@ -33243,7 +33275,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="533" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="533" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A533" s="1" t="s">
         <v>2667</v>
       </c>
@@ -33284,7 +33316,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="534" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="534" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A534" s="1" t="s">
         <v>2672</v>
       </c>
@@ -33325,7 +33357,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="535" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="535" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A535" s="1" t="s">
         <v>2677</v>
       </c>
@@ -33366,7 +33398,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="536" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="536" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A536" s="1" t="s">
         <v>2682</v>
       </c>
@@ -33407,7 +33439,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="537" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="537" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A537" s="1" t="s">
         <v>2687</v>
       </c>
@@ -33448,7 +33480,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="538" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="538" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A538" s="1" t="s">
         <v>2692</v>
       </c>
@@ -33489,7 +33521,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="539" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="539" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A539" s="1" t="s">
         <v>2697</v>
       </c>
@@ -33530,7 +33562,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="540" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="540" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A540" s="1" t="s">
         <v>2702</v>
       </c>
@@ -33571,7 +33603,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="541" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="541" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A541" s="1" t="s">
         <v>2707</v>
       </c>
@@ -33612,7 +33644,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="542" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="542" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A542" s="1" t="s">
         <v>2712</v>
       </c>
@@ -33653,7 +33685,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="543" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="543" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A543" s="1" t="s">
         <v>2717</v>
       </c>
@@ -33694,7 +33726,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="544" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="544" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A544" s="1" t="s">
         <v>2722</v>
       </c>
@@ -33735,7 +33767,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="545" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="545" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A545" s="1" t="s">
         <v>2727</v>
       </c>
@@ -33776,7 +33808,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="546" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="546" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A546" s="1" t="s">
         <v>2732</v>
       </c>
@@ -33817,7 +33849,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="547" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="547" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A547" s="1" t="s">
         <v>2737</v>
       </c>
@@ -33858,7 +33890,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="548" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="548" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A548" s="1" t="s">
         <v>2742</v>
       </c>
@@ -33899,7 +33931,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="549" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="549" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A549" s="1" t="s">
         <v>2747</v>
       </c>
@@ -33940,7 +33972,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="550" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="550" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A550" s="1" t="s">
         <v>2752</v>
       </c>
@@ -33981,7 +34013,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="551" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="551" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A551" s="1" t="s">
         <v>2757</v>
       </c>
@@ -34022,7 +34054,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="552" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="552" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A552" s="1" t="s">
         <v>2762</v>
       </c>
@@ -34063,7 +34095,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="553" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="553" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A553" s="1" t="s">
         <v>2767</v>
       </c>
@@ -34104,7 +34136,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="554" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="554" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A554" s="1" t="s">
         <v>2772</v>
       </c>
@@ -34145,7 +34177,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="555" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="555" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A555" s="1" t="s">
         <v>2777</v>
       </c>
@@ -34186,7 +34218,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="556" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="556" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A556" s="1" t="s">
         <v>2782</v>
       </c>
@@ -34227,7 +34259,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="557" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="557" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A557" s="1" t="s">
         <v>2787</v>
       </c>
@@ -34268,7 +34300,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="558" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="558" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A558" s="1" t="s">
         <v>2792</v>
       </c>
@@ -34309,7 +34341,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="559" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="559" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A559" s="1" t="s">
         <v>2797</v>
       </c>
@@ -34350,7 +34382,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="560" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="560" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A560" s="1" t="s">
         <v>2802</v>
       </c>
@@ -34391,7 +34423,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="561" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="561" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A561" s="1" t="s">
         <v>2805</v>
       </c>
@@ -34432,7 +34464,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="562" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="562" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A562" s="1" t="s">
         <v>2810</v>
       </c>
@@ -34473,7 +34505,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="563" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="563" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A563" s="1" t="s">
         <v>2815</v>
       </c>
@@ -34514,7 +34546,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="564" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="564" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A564" s="1" t="s">
         <v>2820</v>
       </c>
@@ -34555,7 +34587,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="565" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="565" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A565" s="1" t="s">
         <v>2825</v>
       </c>
@@ -34596,7 +34628,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="566" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="566" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A566" s="1" t="s">
         <v>2830</v>
       </c>
@@ -34637,7 +34669,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="567" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="567" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A567" s="1" t="s">
         <v>2835</v>
       </c>
@@ -34678,7 +34710,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="568" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="568" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A568" s="1" t="s">
         <v>2840</v>
       </c>
@@ -34719,7 +34751,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="569" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="569" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A569" s="1" t="s">
         <v>2845</v>
       </c>
@@ -34760,7 +34792,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="570" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="570" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A570" s="1" t="s">
         <v>2850</v>
       </c>
@@ -34801,7 +34833,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="571" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="571" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A571" s="1" t="s">
         <v>2855</v>
       </c>
@@ -34842,7 +34874,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="572" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="572" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A572" s="1" t="s">
         <v>2860</v>
       </c>
@@ -34883,7 +34915,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="573" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="573" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A573" s="1" t="s">
         <v>2865</v>
       </c>
@@ -34924,7 +34956,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="574" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="574" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A574" s="1" t="s">
         <v>2870</v>
       </c>
@@ -34965,7 +34997,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="575" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="575" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A575" s="1" t="s">
         <v>2875</v>
       </c>
@@ -35006,7 +35038,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="576" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="576" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A576" s="1" t="s">
         <v>2880</v>
       </c>
@@ -35047,7 +35079,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="577" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="577" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A577" s="1" t="s">
         <v>2885</v>
       </c>
@@ -35088,7 +35120,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="578" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="578" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A578" s="1" t="s">
         <v>2890</v>
       </c>
@@ -35129,7 +35161,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="579" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="579" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A579" s="1" t="s">
         <v>2895</v>
       </c>
@@ -35170,7 +35202,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="580" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="580" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A580" s="1" t="s">
         <v>2900</v>
       </c>
@@ -35211,7 +35243,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="581" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="581" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A581" s="1" t="s">
         <v>2905</v>
       </c>
@@ -35252,7 +35284,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="582" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="582" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A582" s="1" t="s">
         <v>2910</v>
       </c>
@@ -35293,7 +35325,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="583" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="583" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A583" s="1" t="s">
         <v>2915</v>
       </c>
@@ -35334,7 +35366,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="584" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="584" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A584" s="1" t="s">
         <v>2920</v>
       </c>
@@ -35375,7 +35407,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="585" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="585" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A585" s="1" t="s">
         <v>2925</v>
       </c>
@@ -35416,7 +35448,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="586" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="586" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A586" s="1" t="s">
         <v>2930</v>
       </c>
@@ -35457,7 +35489,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="587" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="587" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A587" s="1" t="s">
         <v>2935</v>
       </c>
@@ -35498,7 +35530,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="588" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="588" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A588" s="1" t="s">
         <v>2940</v>
       </c>
@@ -35539,7 +35571,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="589" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="589" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A589" s="1" t="s">
         <v>2945</v>
       </c>
@@ -35580,7 +35612,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="590" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="590" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A590" s="1" t="s">
         <v>2950</v>
       </c>
@@ -35621,7 +35653,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="591" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="591" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A591" s="1" t="s">
         <v>2955</v>
       </c>
@@ -35662,7 +35694,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="592" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="592" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A592" s="1" t="s">
         <v>2960</v>
       </c>
@@ -35703,7 +35735,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="593" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="593" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A593" s="1" t="s">
         <v>2965</v>
       </c>
@@ -35744,7 +35776,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="594" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="594" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A594" s="1" t="s">
         <v>2970</v>
       </c>
@@ -35785,7 +35817,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="595" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="595" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A595" s="1" t="s">
         <v>2975</v>
       </c>
@@ -35826,7 +35858,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="596" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="596" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A596" s="1" t="s">
         <v>2980</v>
       </c>
@@ -35867,7 +35899,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="597" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="597" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A597" s="1" t="s">
         <v>2985</v>
       </c>
@@ -35908,7 +35940,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="598" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="598" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A598" s="1" t="s">
         <v>2990</v>
       </c>
@@ -35949,7 +35981,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="599" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="599" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A599" s="1" t="s">
         <v>2995</v>
       </c>
@@ -35990,7 +36022,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="600" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="600" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A600" s="1" t="s">
         <v>3000</v>
       </c>
@@ -36031,7 +36063,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="601" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="601" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A601" s="1" t="s">
         <v>3005</v>
       </c>
@@ -36072,7 +36104,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="602" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="602" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A602" s="1" t="s">
         <v>3010</v>
       </c>
@@ -36113,7 +36145,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="603" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="603" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A603" s="1" t="s">
         <v>3015</v>
       </c>
@@ -36154,7 +36186,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="604" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="604" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A604" s="1" t="s">
         <v>3020</v>
       </c>
@@ -36195,7 +36227,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="605" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="605" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A605" s="1" t="s">
         <v>3025</v>
       </c>
@@ -36236,7 +36268,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="606" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="606" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A606" s="1" t="s">
         <v>3030</v>
       </c>
@@ -36277,7 +36309,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="607" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="607" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A607" s="1" t="s">
         <v>3035</v>
       </c>
@@ -36318,7 +36350,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="608" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="608" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A608" s="1" t="s">
         <v>3040</v>
       </c>
@@ -36359,7 +36391,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="609" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="609" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A609" s="1" t="s">
         <v>3045</v>
       </c>
@@ -36400,7 +36432,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="610" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="610" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A610" s="1" t="s">
         <v>3050</v>
       </c>
@@ -36441,7 +36473,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="611" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="611" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A611" s="1" t="s">
         <v>3055</v>
       </c>
@@ -36482,7 +36514,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="612" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="612" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A612" s="1" t="s">
         <v>3060</v>
       </c>
@@ -36523,7 +36555,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="613" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="613" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A613" s="1" t="s">
         <v>3065</v>
       </c>
@@ -36564,7 +36596,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="614" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="614" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A614" s="1" t="s">
         <v>3070</v>
       </c>
@@ -36605,7 +36637,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="615" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="615" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A615" s="1" t="s">
         <v>3075</v>
       </c>
@@ -36646,7 +36678,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="616" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="616" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A616" s="1" t="s">
         <v>3080</v>
       </c>
@@ -36687,7 +36719,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="617" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="617" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A617" s="1" t="s">
         <v>3085</v>
       </c>
@@ -36728,7 +36760,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="618" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="618" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A618" s="1" t="s">
         <v>3090</v>
       </c>
@@ -36769,7 +36801,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="619" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="619" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A619" s="1" t="s">
         <v>3095</v>
       </c>
@@ -36810,7 +36842,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="620" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="620" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A620" s="1" t="s">
         <v>3100</v>
       </c>
@@ -36851,7 +36883,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="621" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="621" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A621" s="1" t="s">
         <v>3105</v>
       </c>
@@ -36892,7 +36924,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="622" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="622" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A622" s="1" t="s">
         <v>3110</v>
       </c>
@@ -36933,7 +36965,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="623" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="623" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A623" s="1" t="s">
         <v>3115</v>
       </c>
@@ -36974,7 +37006,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="624" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="624" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A624" s="1" t="s">
         <v>3120</v>
       </c>
@@ -37015,7 +37047,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="625" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="625" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A625" s="1" t="s">
         <v>3125</v>
       </c>
@@ -37056,7 +37088,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="626" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="626" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A626" s="1" t="s">
         <v>3130</v>
       </c>
@@ -37097,7 +37129,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="627" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="627" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A627" s="1" t="s">
         <v>3135</v>
       </c>
@@ -37138,7 +37170,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="628" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="628" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A628" s="1" t="s">
         <v>3140</v>
       </c>
@@ -37179,7 +37211,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="629" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="629" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A629" s="1" t="s">
         <v>3145</v>
       </c>
@@ -37220,7 +37252,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="630" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="630" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A630" s="1" t="s">
         <v>3150</v>
       </c>
@@ -37261,7 +37293,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="631" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="631" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A631" s="1" t="s">
         <v>3155</v>
       </c>
@@ -37302,7 +37334,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="632" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="632" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A632" s="1" t="s">
         <v>3160</v>
       </c>
@@ -37343,7 +37375,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="633" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="633" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A633" s="1" t="s">
         <v>3165</v>
       </c>
@@ -37384,7 +37416,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="634" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="634" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A634" s="1" t="s">
         <v>3170</v>
       </c>
@@ -37425,7 +37457,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="635" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="635" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A635" s="1" t="s">
         <v>3175</v>
       </c>
@@ -37466,7 +37498,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="636" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="636" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A636" s="1" t="s">
         <v>3180</v>
       </c>
@@ -37507,7 +37539,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="637" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="637" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A637" s="1" t="s">
         <v>3185</v>
       </c>
@@ -37548,7 +37580,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="638" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="638" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A638" s="1" t="s">
         <v>3190</v>
       </c>
@@ -37589,7 +37621,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="639" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="639" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A639" s="1" t="s">
         <v>3195</v>
       </c>
@@ -37630,7 +37662,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="640" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="640" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A640" s="1" t="s">
         <v>3200</v>
       </c>
@@ -37671,7 +37703,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="641" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="641" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A641" s="1" t="s">
         <v>3205</v>
       </c>
@@ -37712,7 +37744,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="642" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="642" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A642" s="1" t="s">
         <v>3210</v>
       </c>
@@ -37753,7 +37785,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="643" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="643" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A643" s="1" t="s">
         <v>3215</v>
       </c>
@@ -37794,7 +37826,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="644" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="644" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A644" s="1" t="s">
         <v>3220</v>
       </c>
@@ -37835,7 +37867,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="645" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="645" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A645" s="1" t="s">
         <v>3225</v>
       </c>
@@ -37876,7 +37908,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="646" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="646" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A646" s="1" t="s">
         <v>3230</v>
       </c>
@@ -37917,7 +37949,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="647" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="647" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A647" s="1" t="s">
         <v>3235</v>
       </c>
@@ -37958,7 +37990,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="648" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="648" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A648" s="1" t="s">
         <v>3240</v>
       </c>
@@ -37999,7 +38031,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="649" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="649" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A649" s="1" t="s">
         <v>3245</v>
       </c>
@@ -38040,7 +38072,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="650" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="650" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A650" s="1" t="s">
         <v>3250</v>
       </c>
@@ -38081,7 +38113,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="651" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="651" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A651" s="1" t="s">
         <v>3255</v>
       </c>
@@ -38122,7 +38154,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="652" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="652" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A652" s="1" t="s">
         <v>3260</v>
       </c>
@@ -38163,7 +38195,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="653" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="653" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A653" s="1" t="s">
         <v>3265</v>
       </c>
@@ -38204,7 +38236,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="654" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="654" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A654" s="1" t="s">
         <v>3270</v>
       </c>
@@ -38245,7 +38277,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="655" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="655" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A655" s="1" t="s">
         <v>3275</v>
       </c>
@@ -38286,7 +38318,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="656" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="656" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A656" s="1" t="s">
         <v>3280</v>
       </c>
@@ -38327,7 +38359,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="657" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="657" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A657" s="1" t="s">
         <v>3285</v>
       </c>
@@ -38368,7 +38400,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="658" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="658" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A658" s="1" t="s">
         <v>3290</v>
       </c>
@@ -38409,7 +38441,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="659" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="659" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A659" s="1" t="s">
         <v>3295</v>
       </c>
@@ -38450,7 +38482,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="660" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="660" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A660" s="1" t="s">
         <v>3300</v>
       </c>
@@ -38491,7 +38523,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="661" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="661" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A661" s="1" t="s">
         <v>3305</v>
       </c>
@@ -38532,7 +38564,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="662" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="662" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A662" s="1" t="s">
         <v>3310</v>
       </c>
@@ -38573,7 +38605,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="663" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="663" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A663" s="1" t="s">
         <v>3315</v>
       </c>
@@ -38614,7 +38646,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="664" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="664" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A664" s="1" t="s">
         <v>3320</v>
       </c>
@@ -38655,7 +38687,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="665" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="665" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A665" s="1" t="s">
         <v>3325</v>
       </c>
@@ -38696,7 +38728,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="666" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="666" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A666" s="1" t="s">
         <v>3330</v>
       </c>
@@ -38737,7 +38769,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="667" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="667" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A667" s="1" t="s">
         <v>3335</v>
       </c>
@@ -38778,7 +38810,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="668" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="668" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A668" s="1" t="s">
         <v>3340</v>
       </c>
@@ -38819,7 +38851,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="669" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="669" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A669" s="1" t="s">
         <v>3345</v>
       </c>
@@ -38860,7 +38892,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="670" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="670" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A670" s="1" t="s">
         <v>3350</v>
       </c>
@@ -38901,7 +38933,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="671" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="671" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A671" s="1" t="s">
         <v>3355</v>
       </c>
@@ -38942,7 +38974,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="672" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="672" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A672" s="1" t="s">
         <v>3360</v>
       </c>
@@ -38983,7 +39015,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="673" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="673" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A673" s="1" t="s">
         <v>3365</v>
       </c>
@@ -39024,7 +39056,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="674" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="674" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A674" s="1" t="s">
         <v>3370</v>
       </c>
@@ -39065,7 +39097,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="675" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="675" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A675" s="1" t="s">
         <v>3375</v>
       </c>
@@ -39106,7 +39138,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="676" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="676" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A676" s="1" t="s">
         <v>3380</v>
       </c>
@@ -39147,7 +39179,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="677" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="677" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A677" s="1" t="s">
         <v>3385</v>
       </c>
@@ -39188,7 +39220,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="678" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="678" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A678" s="1" t="s">
         <v>3390</v>
       </c>
@@ -39229,7 +39261,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="679" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="679" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A679" s="1" t="s">
         <v>3395</v>
       </c>
@@ -39270,7 +39302,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="680" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="680" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A680" s="1" t="s">
         <v>3400</v>
       </c>
@@ -39311,7 +39343,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="681" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="681" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A681" s="1" t="s">
         <v>3405</v>
       </c>
@@ -39352,7 +39384,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="682" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="682" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A682" s="1" t="s">
         <v>3410</v>
       </c>
@@ -39393,7 +39425,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="683" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="683" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A683" s="1" t="s">
         <v>3415</v>
       </c>
@@ -39434,7 +39466,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="684" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="684" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A684" s="1" t="s">
         <v>3420</v>
       </c>
@@ -39475,7 +39507,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="685" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="685" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A685" s="1" t="s">
         <v>3425</v>
       </c>
@@ -39516,7 +39548,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="686" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="686" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A686" s="1" t="s">
         <v>3430</v>
       </c>
@@ -39557,7 +39589,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="687" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="687" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A687" s="1" t="s">
         <v>3435</v>
       </c>
@@ -39598,7 +39630,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="688" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="688" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A688" s="1" t="s">
         <v>3440</v>
       </c>
@@ -39639,7 +39671,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="689" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="689" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A689" s="1" t="s">
         <v>3445</v>
       </c>
@@ -39680,7 +39712,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="690" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="690" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A690" s="1" t="s">
         <v>3450</v>
       </c>
@@ -39721,7 +39753,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="691" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="691" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A691" s="1" t="s">
         <v>3455</v>
       </c>
@@ -39762,7 +39794,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="692" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="692" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A692" s="1" t="s">
         <v>3460</v>
       </c>
@@ -39803,7 +39835,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="693" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="693" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A693" s="1" t="s">
         <v>3465</v>
       </c>
@@ -39844,7 +39876,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="694" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="694" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A694" s="1" t="s">
         <v>3470</v>
       </c>
@@ -39885,7 +39917,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="695" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="695" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A695" s="1" t="s">
         <v>3475</v>
       </c>
@@ -39926,7 +39958,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="696" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="696" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A696" s="1" t="s">
         <v>3480</v>
       </c>
@@ -39967,7 +39999,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="697" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="697" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A697" s="1" t="s">
         <v>3485</v>
       </c>
@@ -40008,7 +40040,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="698" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="698" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A698" s="1" t="s">
         <v>3490</v>
       </c>
@@ -40049,7 +40081,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="699" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="699" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A699" s="1" t="s">
         <v>3495</v>
       </c>
@@ -40090,7 +40122,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="700" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="700" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A700" s="1" t="s">
         <v>3500</v>
       </c>
@@ -40131,7 +40163,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="701" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="701" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A701" s="1" t="s">
         <v>3505</v>
       </c>
@@ -40172,7 +40204,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="702" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="702" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A702" s="1" t="s">
         <v>3510</v>
       </c>
@@ -40213,7 +40245,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="703" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="703" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A703" s="1" t="s">
         <v>3515</v>
       </c>
@@ -40254,7 +40286,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="704" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="704" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A704" s="1" t="s">
         <v>3520</v>
       </c>
@@ -40295,7 +40327,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="705" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="705" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A705" s="1" t="s">
         <v>3525</v>
       </c>
@@ -40336,7 +40368,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="706" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="706" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A706" s="1" t="s">
         <v>3530</v>
       </c>
@@ -40377,7 +40409,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="707" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="707" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A707" s="1" t="s">
         <v>3535</v>
       </c>
@@ -40418,7 +40450,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="708" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="708" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A708" s="1" t="s">
         <v>3540</v>
       </c>
@@ -40459,7 +40491,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="709" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="709" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A709" s="1" t="s">
         <v>3545</v>
       </c>
@@ -40500,7 +40532,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="710" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="710" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A710" s="1" t="s">
         <v>3550</v>
       </c>
@@ -40541,7 +40573,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="711" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="711" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A711" s="1" t="s">
         <v>3555</v>
       </c>
@@ -40582,7 +40614,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="712" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="712" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A712" s="1" t="s">
         <v>3560</v>
       </c>
@@ -40623,7 +40655,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="713" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="713" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A713" s="1" t="s">
         <v>3565</v>
       </c>
@@ -40664,7 +40696,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="714" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="714" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A714" s="1" t="s">
         <v>3570</v>
       </c>
@@ -40705,7 +40737,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="715" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="715" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A715" s="1" t="s">
         <v>3575</v>
       </c>
@@ -40746,7 +40778,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="716" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="716" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A716" s="1" t="s">
         <v>3580</v>
       </c>
@@ -40787,7 +40819,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="717" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="717" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A717" s="1" t="s">
         <v>3585</v>
       </c>
@@ -40828,7 +40860,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="718" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="718" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A718" s="1" t="s">
         <v>3590</v>
       </c>
@@ -40869,7 +40901,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="719" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="719" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A719" s="1" t="s">
         <v>3595</v>
       </c>
@@ -40910,7 +40942,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="720" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="720" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A720" s="1" t="s">
         <v>3600</v>
       </c>
@@ -40951,7 +40983,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="721" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="721" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A721" s="1" t="s">
         <v>3605</v>
       </c>
@@ -40992,7 +41024,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="722" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="722" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A722" s="1" t="s">
         <v>3610</v>
       </c>
@@ -41033,7 +41065,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="723" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="723" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A723" s="1" t="s">
         <v>3615</v>
       </c>
@@ -41074,7 +41106,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="724" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="724" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A724" s="1" t="s">
         <v>3620</v>
       </c>
@@ -41115,7 +41147,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="725" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="725" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A725" s="1" t="s">
         <v>3625</v>
       </c>
@@ -41156,7 +41188,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="726" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="726" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A726" s="1" t="s">
         <v>3630</v>
       </c>
@@ -41197,7 +41229,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="727" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="727" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A727" s="1">
         <v>2000000001</v>
       </c>
@@ -41232,7 +41264,7 @@
       <c r="L727" s="1"/>
       <c r="M727" s="1"/>
     </row>
-    <row r="728" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="728" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A728" s="1">
         <v>2000000002</v>
       </c>
@@ -41267,7 +41299,7 @@
       <c r="L728" s="1"/>
       <c r="M728" s="1"/>
     </row>
-    <row r="729" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="729" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A729" s="1">
         <v>2000000003</v>
       </c>
@@ -41302,7 +41334,7 @@
       <c r="L729" s="1"/>
       <c r="M729" s="1"/>
     </row>
-    <row r="730" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="730" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A730" s="1">
         <v>2000000004</v>
       </c>
@@ -41337,9 +41369,9 @@
       <c r="L730" s="1"/>
       <c r="M730" s="1"/>
     </row>
-    <row r="731" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="731" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A731" s="1">
-        <v>200000005</v>
+        <v>2000000005</v>
       </c>
       <c r="B731" s="1" t="s">
         <v>3642</v>
@@ -41372,9 +41404,9 @@
       <c r="L731" s="1"/>
       <c r="M731" s="1"/>
     </row>
-    <row r="732" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="732" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A732" s="1">
-        <v>200000006</v>
+        <v>2000000006</v>
       </c>
       <c r="B732" s="1" t="s">
         <v>3642</v>
@@ -41407,9 +41439,9 @@
       <c r="L732" s="1"/>
       <c r="M732" s="1"/>
     </row>
-    <row r="733" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="733" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A733" s="1">
-        <v>200000007</v>
+        <v>2000000007</v>
       </c>
       <c r="B733" s="1" t="s">
         <v>3642</v>
@@ -41442,9 +41474,9 @@
       <c r="L733" s="1"/>
       <c r="M733" s="1"/>
     </row>
-    <row r="734" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="734" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A734" s="1">
-        <v>200000008</v>
+        <v>2000000008</v>
       </c>
       <c r="B734" s="1" t="s">
         <v>3642</v>
@@ -41476,6 +41508,146 @@
       <c r="K734" s="1"/>
       <c r="L734" s="1"/>
       <c r="M734" s="1"/>
+    </row>
+    <row r="735" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A735" s="1">
+        <v>2000000009</v>
+      </c>
+      <c r="B735" s="1" t="s">
+        <v>3642</v>
+      </c>
+      <c r="C735" s="1" t="s">
+        <v>3652</v>
+      </c>
+      <c r="D735" s="2" t="s">
+        <v>3653</v>
+      </c>
+      <c r="E735" s="2">
+        <v>121.444195280958</v>
+      </c>
+      <c r="F735" s="2">
+        <v>25.052854327866701</v>
+      </c>
+      <c r="G735" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H735" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I735" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J735" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K735" s="1"/>
+      <c r="L735" s="1"/>
+      <c r="M735" s="1"/>
+    </row>
+    <row r="736" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A736" s="1">
+        <v>2000000010</v>
+      </c>
+      <c r="B736" s="1" t="s">
+        <v>3642</v>
+      </c>
+      <c r="C736" s="1" t="s">
+        <v>3654</v>
+      </c>
+      <c r="D736" s="2" t="s">
+        <v>3655</v>
+      </c>
+      <c r="E736" s="2">
+        <v>121.49214058095799</v>
+      </c>
+      <c r="F736" s="2">
+        <v>25.083439869317299</v>
+      </c>
+      <c r="G736" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H736" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I736" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J736" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K736" s="1"/>
+      <c r="L736" s="1"/>
+      <c r="M736" s="1"/>
+    </row>
+    <row r="737" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A737" s="1">
+        <v>2000000011</v>
+      </c>
+      <c r="B737" s="1" t="s">
+        <v>3642</v>
+      </c>
+      <c r="C737" s="1" t="s">
+        <v>3656</v>
+      </c>
+      <c r="D737" s="2" t="s">
+        <v>3659</v>
+      </c>
+      <c r="E737" s="2">
+        <v>121.39557825718801</v>
+      </c>
+      <c r="F737" s="2">
+        <v>25.077620425910698</v>
+      </c>
+      <c r="G737" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H737" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I737" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J737" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K737" s="1"/>
+      <c r="L737" s="1"/>
+      <c r="M737" s="1"/>
+    </row>
+    <row r="738" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A738" s="1">
+        <v>2000000012</v>
+      </c>
+      <c r="B738" s="1" t="s">
+        <v>3642</v>
+      </c>
+      <c r="C738" s="1" t="s">
+        <v>3657</v>
+      </c>
+      <c r="D738" s="2" t="s">
+        <v>3658</v>
+      </c>
+      <c r="E738" s="2">
+        <v>121.510106655812</v>
+      </c>
+      <c r="F738" s="2">
+        <v>25.120041515438199</v>
+      </c>
+      <c r="G738" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H738" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I738" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J738" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K738" s="1"/>
+      <c r="L738" s="1"/>
+      <c r="M738" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
@@ -41486,7 +41658,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.149999999999999" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -41496,7 +41668,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.149999999999999" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
